--- a/tests/perf_v2/perf_history/v2.5/semantic_segmentation/SEMANTIC_SEGMENTATION-raw-small_aerial.xlsx
+++ b/tests/perf_v2/perf_history/v2.5/semantic_segmentation/SEMANTIC_SEGMENTATION-raw-small_aerial.xlsx
@@ -591,56 +591,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C2" t="n">
-        <v>19.38499450683594</v>
+        <v>24.20329546928406</v>
       </c>
       <c r="D2" t="n">
-        <v>1.169999957084656</v>
+        <v>1.159999966621399</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0560335086658596</v>
+        <v>0.0562944149908919</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5126389265060425</v>
+        <v>0.5385844707489014</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5152122378349304</v>
+        <v>0.5363255739212036</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5148237943649292</v>
+        <v>0.5365433692932129</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5119996070861816</v>
+        <v>0.5355786085128784</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0432861819863319</v>
+        <v>0.0424073226749897</v>
       </c>
       <c r="K2" t="n">
-        <v>37.35372066497803</v>
+        <v>30.9040105342865</v>
       </c>
       <c r="L2" t="n">
-        <v>1.120428323745728</v>
+        <v>1.185202360153198</v>
       </c>
       <c r="M2" t="n">
-        <v>8.186904907226562</v>
+        <v>8.66538143157959</v>
       </c>
       <c r="N2" t="n">
-        <v>8.484407186508179</v>
+        <v>9.642174482345579</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0373476107915242</v>
+        <v>0.0395067453384399</v>
       </c>
       <c r="P2" t="n">
-        <v>0.2728968302408854</v>
+        <v>0.2888460477193196</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.282813572883606</v>
+        <v>0.321405816078186</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250701-121543</t>
+          <t>20250720-050116</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -665,22 +665,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -690,10 +690,10 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -712,56 +712,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C3" t="n">
-        <v>19.00569415092468</v>
+        <v>23.73980832099915</v>
       </c>
       <c r="D3" t="n">
-        <v>1.159999966621399</v>
+        <v>1.169999957084656</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0558967300151523</v>
+        <v>0.0554243647493421</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5329964160919189</v>
+        <v>0.5237066149711609</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5357258319854736</v>
+        <v>0.5276978015899658</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5362974405288696</v>
+        <v>0.5273638367652893</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5352541208267212</v>
+        <v>0.5271754264831543</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0419990234076976</v>
+        <v>0.0418689399957656</v>
       </c>
       <c r="K3" t="n">
-        <v>30.327388048172</v>
+        <v>30.8991858959198</v>
       </c>
       <c r="L3" t="n">
-        <v>1.149303913116455</v>
+        <v>1.194629669189453</v>
       </c>
       <c r="M3" t="n">
-        <v>8.377992868423462</v>
+        <v>8.759116649627686</v>
       </c>
       <c r="N3" t="n">
-        <v>10.02319884300232</v>
+        <v>9.355445146560667</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0383101304372151</v>
+        <v>0.0398209889729817</v>
       </c>
       <c r="P3" t="n">
-        <v>0.2792664289474487</v>
+        <v>0.2919705549875895</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.3341066281000773</v>
+        <v>0.3118481715520223</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250701-121747</t>
+          <t>20250720-050322</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -786,22 +786,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -811,10 +811,10 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -836,53 +836,53 @@
         <v>19</v>
       </c>
       <c r="C4" t="n">
-        <v>19.50011563301086</v>
+        <v>19.5289077758789</v>
       </c>
       <c r="D4" t="n">
         <v>1.159999966621399</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0562509643404107</v>
+        <v>0.0561105559923146</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5228339433670044</v>
+        <v>0.5217826366424561</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5276827812194824</v>
+        <v>0.523837149143219</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5277941823005676</v>
+        <v>0.5236536860466003</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5272358655929565</v>
+        <v>0.5219542384147644</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0448940433561801</v>
+        <v>0.0440789237618446</v>
       </c>
       <c r="K4" t="n">
-        <v>29.82626605033875</v>
+        <v>30.65856432914734</v>
       </c>
       <c r="L4" t="n">
-        <v>1.148728370666504</v>
+        <v>1.250608444213867</v>
       </c>
       <c r="M4" t="n">
-        <v>8.891881227493286</v>
+        <v>8.738326072692871</v>
       </c>
       <c r="N4" t="n">
-        <v>8.547922849655151</v>
+        <v>9.201722621917725</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0382909456888834</v>
+        <v>0.0416869481404622</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2963960409164429</v>
+        <v>0.291277535756429</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.2849307616551717</v>
+        <v>0.3067240873972575</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250701-121945</t>
+          <t>20250720-050526</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -907,22 +907,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -932,10 +932,10 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -945,7 +945,7 @@
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -954,56 +954,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C5" t="n">
-        <v>19.58806324005127</v>
+        <v>19.61807084083557</v>
       </c>
       <c r="D5" t="n">
         <v>1.159999966621399</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0558330817148089</v>
+        <v>0.0559926191835026</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5371459722518921</v>
+        <v>0.5383193492889404</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5376995801925659</v>
+        <v>0.539786696434021</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5375270843505859</v>
+        <v>0.5400868058204651</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5358278155326843</v>
+        <v>0.5393303632736206</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0416197627782821</v>
+        <v>0.0440717861056327</v>
       </c>
       <c r="K5" t="n">
-        <v>29.89713335037231</v>
+        <v>30.86731338500977</v>
       </c>
       <c r="L5" t="n">
-        <v>1.153649568557739</v>
+        <v>1.24501895904541</v>
       </c>
       <c r="M5" t="n">
-        <v>8.736501455307007</v>
+        <v>8.823449850082397</v>
       </c>
       <c r="N5" t="n">
-        <v>8.699187994003296</v>
+        <v>9.043648242950439</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0384549856185913</v>
+        <v>0.0415006319681803</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2912167151769002</v>
+        <v>0.2941149950027465</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.2899729331334432</v>
+        <v>0.3014549414316813</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250701-122142</t>
+          <t>20250720-050727</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1028,22 +1028,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1053,10 +1053,10 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1066,7 +1066,7 @@
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -1075,56 +1075,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="C6" t="n">
-        <v>22.85135984420776</v>
+        <v>35.29046177864075</v>
       </c>
       <c r="D6" t="n">
-        <v>1.159999966621399</v>
+        <v>1.360000014305115</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0562312034890055</v>
+        <v>0.056716166022751</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5279930830001831</v>
+        <v>0.5454379320144653</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5313175320625305</v>
+        <v>0.5506823658943176</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5315635800361633</v>
+        <v>0.5506055951118469</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5311087965965271</v>
+        <v>0.5491693019866943</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0431768409907817</v>
+        <v>0.0414758846163749</v>
       </c>
       <c r="K6" t="n">
-        <v>30.26500344276428</v>
+        <v>30.85289001464844</v>
       </c>
       <c r="L6" t="n">
-        <v>1.158488988876343</v>
+        <v>1.217617750167847</v>
       </c>
       <c r="M6" t="n">
-        <v>8.294044017791748</v>
+        <v>8.998705387115479</v>
       </c>
       <c r="N6" t="n">
-        <v>8.77274489402771</v>
+        <v>9.269238710403442</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0386162996292114</v>
+        <v>0.0405872583389282</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2764681339263916</v>
+        <v>0.2999568462371826</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.2924248298009236</v>
+        <v>0.3089746236801147</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250701-122340</t>
+          <t>20250720-050927</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1149,22 +1149,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1174,10 +1174,10 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -1362,56 +1362,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>20</v>
+        <v>68</v>
       </c>
       <c r="C2" t="n">
-        <v>33.5852575302124</v>
+        <v>111.1647372245789</v>
       </c>
       <c r="D2" t="n">
-        <v>3.009999990463257</v>
+        <v>3.059999942779541</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1411263763904571</v>
+        <v>0.1528739098678616</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1898376643657684</v>
+        <v>0.3940041065216064</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2101011574268341</v>
+        <v>0.40372234582901</v>
       </c>
       <c r="H2" t="n">
-        <v>0.21004518866539</v>
+        <v>0.4021303355693817</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2109699696302414</v>
+        <v>0.3905501961708069</v>
       </c>
       <c r="J2" t="n">
-        <v>0.07121289521455761</v>
+        <v>0.077861376106739</v>
       </c>
       <c r="K2" t="n">
-        <v>66.53018569946289</v>
+        <v>68.02818703651428</v>
       </c>
       <c r="L2" t="n">
-        <v>1.557652711868286</v>
+        <v>1.6501784324646</v>
       </c>
       <c r="M2" t="n">
-        <v>9.744253873825071</v>
+        <v>9.393870830535889</v>
       </c>
       <c r="N2" t="n">
-        <v>16.04455947875977</v>
+        <v>11.79795479774475</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0519217570622762</v>
+        <v>0.0550059477488199</v>
       </c>
       <c r="P2" t="n">
-        <v>0.3248084624608358</v>
+        <v>0.3131290276845296</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.5348186492919922</v>
+        <v>0.393265159924825</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250630-122753</t>
+          <t>20250718-085434</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -1436,22 +1436,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -1461,10 +1461,10 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -1483,56 +1483,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="C3" t="n">
-        <v>32.31888914108276</v>
+        <v>73.73867893218994</v>
       </c>
       <c r="D3" t="n">
-        <v>3.009999990463257</v>
+        <v>3.059999942779541</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1400559815137009</v>
+        <v>0.1517002006823365</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1821017563343048</v>
+        <v>0.2837473154067993</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2014259546995163</v>
+        <v>0.2961084246635437</v>
       </c>
       <c r="H3" t="n">
-        <v>0.201675146818161</v>
+        <v>0.295762687921524</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2026022523641586</v>
+        <v>0.2920447289943695</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0707014426589012</v>
+        <v>0.07283768802881239</v>
       </c>
       <c r="K3" t="n">
-        <v>66.98098731040955</v>
+        <v>61.34244108200073</v>
       </c>
       <c r="L3" t="n">
-        <v>1.650994539260864</v>
+        <v>1.640236616134644</v>
       </c>
       <c r="M3" t="n">
-        <v>11.01160407066345</v>
+        <v>9.05840229988098</v>
       </c>
       <c r="N3" t="n">
-        <v>12.86078262329102</v>
+        <v>11.21808004379272</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0550331513086954</v>
+        <v>0.0546745538711547</v>
       </c>
       <c r="P3" t="n">
-        <v>0.367053469022115</v>
+        <v>0.301946743329366</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.4286927541097005</v>
+        <v>0.3739360014597574</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250630-123044</t>
+          <t>20250718-085841</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -1557,22 +1557,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -1582,10 +1582,10 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -1604,56 +1604,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="C4" t="n">
-        <v>33.08188581466675</v>
+        <v>54.31889677047729</v>
       </c>
       <c r="D4" t="n">
-        <v>3.009999990463257</v>
+        <v>3.059999942779541</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1387496046721935</v>
+        <v>0.1504291528835892</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2031495571136474</v>
+        <v>0.2240137159824371</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2069001197814941</v>
+        <v>0.2340574860572815</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2064078897237777</v>
+        <v>0.234003409743309</v>
       </c>
       <c r="I4" t="n">
-        <v>0.206841304898262</v>
+        <v>0.2341594845056533</v>
       </c>
       <c r="J4" t="n">
-        <v>0.07219880074262611</v>
+        <v>0.0726764872670173</v>
       </c>
       <c r="K4" t="n">
-        <v>65.1354603767395</v>
+        <v>66.88103699684143</v>
       </c>
       <c r="L4" t="n">
-        <v>1.535556793212891</v>
+        <v>1.93265151977539</v>
       </c>
       <c r="M4" t="n">
-        <v>8.44703483581543</v>
+        <v>9.733065366744995</v>
       </c>
       <c r="N4" t="n">
-        <v>11.88303709030151</v>
+        <v>11.84351658821106</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0511852264404296</v>
+        <v>0.0644217173258463</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2815678278605143</v>
+        <v>0.3244355122248332</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.3961012363433838</v>
+        <v>0.394783886273702</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250630-123333</t>
+          <t>20250718-090229</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1678,22 +1678,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1703,10 +1703,10 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1716,7 +1716,7 @@
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -1725,56 +1725,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>19</v>
+        <v>60</v>
       </c>
       <c r="C5" t="n">
-        <v>32.43941712379456</v>
+        <v>98.93816041946413</v>
       </c>
       <c r="D5" t="n">
-        <v>3.009999990463257</v>
+        <v>3.059999942779541</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1398664595265137</v>
+        <v>0.1516955092549323</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1925333142280578</v>
+        <v>0.3783194124698639</v>
       </c>
       <c r="G5" t="n">
-        <v>0.204362466931343</v>
+        <v>0.3858546614646911</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2046160101890564</v>
+        <v>0.3854338824748993</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1988957226276397</v>
+        <v>0.3790627717971802</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0672017857432365</v>
+        <v>0.0707963481545448</v>
       </c>
       <c r="K5" t="n">
-        <v>65.21082806587219</v>
+        <v>61.28239011764526</v>
       </c>
       <c r="L5" t="n">
-        <v>1.574831485748291</v>
+        <v>1.648331642150879</v>
       </c>
       <c r="M5" t="n">
-        <v>8.733902931213379</v>
+        <v>9.517051458358765</v>
       </c>
       <c r="N5" t="n">
-        <v>12.82640480995178</v>
+        <v>11.57126593589783</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0524943828582763</v>
+        <v>0.0549443880716959</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2911300977071126</v>
+        <v>0.3172350486119588</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.4275468269983927</v>
+        <v>0.3857088645299276</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250630-123637</t>
+          <t>20250718-090559</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1799,22 +1799,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1824,10 +1824,10 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1837,7 +1837,7 @@
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -1846,56 +1846,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C6" t="n">
-        <v>32.22344040870667</v>
+        <v>35.50347399711609</v>
       </c>
       <c r="D6" t="n">
-        <v>3.009999990463257</v>
+        <v>3.059999942779541</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1413874328136443</v>
+        <v>0.151647450774908</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1730355471372604</v>
+        <v>0.168219968676567</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1824037879705429</v>
+        <v>0.1730631291866302</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1824134290218353</v>
+        <v>0.1736255288124084</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1819790154695511</v>
+        <v>0.1659233570098877</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0739552676677703</v>
+        <v>0.07776191830635069</v>
       </c>
       <c r="K6" t="n">
-        <v>59.35964775085449</v>
+        <v>67.40379190444946</v>
       </c>
       <c r="L6" t="n">
-        <v>1.615649938583374</v>
+        <v>1.665375947952271</v>
       </c>
       <c r="M6" t="n">
-        <v>8.799666881561279</v>
+        <v>9.123697519302368</v>
       </c>
       <c r="N6" t="n">
-        <v>11.87292575836182</v>
+        <v>12.47004318237305</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0538549979527791</v>
+        <v>0.055512531598409</v>
       </c>
       <c r="P6" t="n">
-        <v>0.293322229385376</v>
+        <v>0.3041232506434123</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.3957641919453938</v>
+        <v>0.4156681060791015</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250630-123922</t>
+          <t>20250718-091013</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1920,22 +1920,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1945,10 +1945,10 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1958,7 +1958,7 @@
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -2133,56 +2133,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="C2" t="n">
-        <v>27.54608607292176</v>
+        <v>46.78793907165527</v>
       </c>
       <c r="D2" t="n">
         <v>1.440000057220459</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1134289146253936</v>
+        <v>0.1227402123622596</v>
       </c>
       <c r="F2" t="n">
-        <v>0.167014479637146</v>
+        <v>0.2207955420017242</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1728498041629791</v>
+        <v>0.2269479781389236</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1726974546909332</v>
+        <v>0.2270411849021911</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1262219250202179</v>
+        <v>0.1924721896648407</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0671450793743133</v>
+        <v>0.0669071972370147</v>
       </c>
       <c r="K2" t="n">
-        <v>55.19316983222961</v>
+        <v>51.28772115707397</v>
       </c>
       <c r="L2" t="n">
-        <v>1.392437696456909</v>
+        <v>1.402185916900635</v>
       </c>
       <c r="M2" t="n">
-        <v>12.902263879776</v>
+        <v>13.5505805015564</v>
       </c>
       <c r="N2" t="n">
-        <v>15.5020751953125</v>
+        <v>16.71355009078979</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0464145898818969</v>
+        <v>0.0467395305633544</v>
       </c>
       <c r="P2" t="n">
-        <v>0.4300754626592</v>
+        <v>0.4516860167185465</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.51673583984375</v>
+        <v>0.5571183363596598</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250630-153321</t>
+          <t>20250718-150326</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -2207,22 +2207,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -2232,10 +2232,10 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -2245,7 +2245,7 @@
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -2254,56 +2254,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="C3" t="n">
-        <v>27.94537281990052</v>
+        <v>62.36910271644592</v>
       </c>
       <c r="D3" t="n">
         <v>1.440000057220459</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1172437754116559</v>
+        <v>0.1222115951505573</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1696836352348327</v>
+        <v>0.2518113851547241</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1894402801990509</v>
+        <v>0.2612974047660827</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1890288740396499</v>
+        <v>0.2613295912742615</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1495736837387085</v>
+        <v>0.2256472408771515</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0604374259710311</v>
+        <v>0.0607125274837017</v>
       </c>
       <c r="K3" t="n">
-        <v>54.37360239028931</v>
+        <v>56.9702627658844</v>
       </c>
       <c r="L3" t="n">
-        <v>1.353684425354004</v>
+        <v>1.464324951171875</v>
       </c>
       <c r="M3" t="n">
-        <v>12.75267767906189</v>
+        <v>13.24821376800537</v>
       </c>
       <c r="N3" t="n">
-        <v>16.12561821937561</v>
+        <v>18.0265588760376</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0451228141784667</v>
+        <v>0.0488108317057291</v>
       </c>
       <c r="P3" t="n">
-        <v>0.4250892559687296</v>
+        <v>0.441607125600179</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.5375206073125204</v>
+        <v>0.6008852958679199</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250630-153617</t>
+          <t>20250718-150646</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -2328,22 +2328,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -2353,10 +2353,10 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -2366,7 +2366,7 @@
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -2375,56 +2375,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="C4" t="n">
-        <v>28.3547511100769</v>
+        <v>51.66034197807312</v>
       </c>
       <c r="D4" t="n">
         <v>1.440000057220459</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1190970806699049</v>
+        <v>0.1232822651250494</v>
       </c>
       <c r="F4" t="n">
-        <v>0.173920452594757</v>
+        <v>0.2376798391342163</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1790376752614975</v>
+        <v>0.2676172852516174</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1784390360116958</v>
+        <v>0.2677917182445526</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1519238948822021</v>
+        <v>0.1979610919952392</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0610939972102642</v>
+        <v>0.0604877322912216</v>
       </c>
       <c r="K4" t="n">
-        <v>55.15815496444702</v>
+        <v>56.51408267021179</v>
       </c>
       <c r="L4" t="n">
-        <v>1.312053442001343</v>
+        <v>1.442362785339356</v>
       </c>
       <c r="M4" t="n">
-        <v>12.7907600402832</v>
+        <v>13.83525156974792</v>
       </c>
       <c r="N4" t="n">
-        <v>17.24239826202393</v>
+        <v>16.67727589607239</v>
       </c>
       <c r="O4" t="n">
-        <v>0.043735114733378</v>
+        <v>0.0480787595113118</v>
       </c>
       <c r="P4" t="n">
-        <v>0.4263586680094401</v>
+        <v>0.4611750523249308</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.5747466087341309</v>
+        <v>0.5559091965357462</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250630-153854</t>
+          <t>20250718-151023</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -2449,22 +2449,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -2474,10 +2474,10 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -2496,56 +2496,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="C5" t="n">
-        <v>27.84213781356812</v>
+        <v>57.88482165336609</v>
       </c>
       <c r="D5" t="n">
-        <v>1.440000057220459</v>
+        <v>1.450000047683716</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1173358092966832</v>
+        <v>0.1240976203233003</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1622088551521301</v>
+        <v>0.2297760248184204</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1684309393167495</v>
+        <v>0.2367852330207824</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1683761924505233</v>
+        <v>0.2366120219230651</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1432925015687942</v>
+        <v>0.1022445112466812</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0571042075753212</v>
+        <v>0.0606279037892818</v>
       </c>
       <c r="K5" t="n">
-        <v>55.2349157333374</v>
+        <v>56.99233818054199</v>
       </c>
       <c r="L5" t="n">
-        <v>1.380147218704224</v>
+        <v>1.515407562255859</v>
       </c>
       <c r="M5" t="n">
-        <v>12.58212685585022</v>
+        <v>13.45753502845764</v>
       </c>
       <c r="N5" t="n">
-        <v>17.43665766716003</v>
+        <v>16.64229702949524</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0460049072901407</v>
+        <v>0.0505135854085286</v>
       </c>
       <c r="P5" t="n">
-        <v>0.4194042285283406</v>
+        <v>0.448584500948588</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.5812219222386678</v>
+        <v>0.554743234316508</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250630-154132</t>
+          <t>20250718-151348</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -2570,22 +2570,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -2595,10 +2595,10 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -2608,7 +2608,7 @@
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -2617,56 +2617,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="C6" t="n">
-        <v>28.03087329864502</v>
+        <v>52.87658858299256</v>
       </c>
       <c r="D6" t="n">
         <v>1.440000057220459</v>
       </c>
       <c r="E6" t="n">
-        <v>0.112558428394167</v>
+        <v>0.1270229135536484</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1692633926868438</v>
+        <v>0.2256554961204528</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1778790056705474</v>
+        <v>0.2267203330993652</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1778585463762283</v>
+        <v>0.2269483506679535</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1648772656917572</v>
+        <v>0.1760870814323425</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0645749568939209</v>
+        <v>0.0624355152249336</v>
       </c>
       <c r="K6" t="n">
-        <v>54.8952648639679</v>
+        <v>56.4743390083313</v>
       </c>
       <c r="L6" t="n">
-        <v>1.349071502685547</v>
+        <v>1.51559591293335</v>
       </c>
       <c r="M6" t="n">
-        <v>12.75232839584351</v>
+        <v>13.75158405303955</v>
       </c>
       <c r="N6" t="n">
-        <v>15.79143834114075</v>
+        <v>16.72890281677246</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0449690500895182</v>
+        <v>0.0505198637644449</v>
       </c>
       <c r="P6" t="n">
-        <v>0.4250776131947835</v>
+        <v>0.4583861351013183</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.5263812780380249</v>
+        <v>0.5576300938924154</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250630-154410</t>
+          <t>20250718-151719</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -2691,22 +2691,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -2716,10 +2716,10 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -2729,7 +2729,7 @@
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -2904,56 +2904,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>19</v>
+        <v>60</v>
       </c>
       <c r="C2" t="n">
-        <v>59.92318916320801</v>
+        <v>179.4314470291138</v>
       </c>
       <c r="D2" t="n">
-        <v>8.909999847412109</v>
+        <v>8.949999809265137</v>
       </c>
       <c r="E2" t="n">
-        <v>0.326078662746831</v>
+        <v>0.3305132125814756</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1764462143182754</v>
+        <v>0.3001717031002044</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1851011216640472</v>
+        <v>0.3078881502151489</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1852739304304123</v>
+        <v>0.3071324527263641</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1336687356233596</v>
+        <v>0.1267274320125579</v>
       </c>
       <c r="J2" t="n">
-        <v>0.117179237306118</v>
+        <v>0.1184577494859695</v>
       </c>
       <c r="K2" t="n">
-        <v>345.1965086460113</v>
+        <v>352.863795042038</v>
       </c>
       <c r="L2" t="n">
-        <v>2.342900514602661</v>
+        <v>2.719746112823486</v>
       </c>
       <c r="M2" t="n">
-        <v>12.53277492523193</v>
+        <v>13.47654557228088</v>
       </c>
       <c r="N2" t="n">
-        <v>21.3858630657196</v>
+        <v>20.81514549255371</v>
       </c>
       <c r="O2" t="n">
-        <v>0.07809668382008871</v>
+        <v>0.0906582037607828</v>
       </c>
       <c r="P2" t="n">
-        <v>0.4177591641743978</v>
+        <v>0.4492181857426961</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.7128621021906535</v>
+        <v>0.6938381830851237</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250630-185933</t>
+          <t>20250718-211635</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -2978,22 +2978,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -3003,10 +3003,10 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -3025,56 +3025,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19</v>
+        <v>52</v>
       </c>
       <c r="C3" t="n">
-        <v>59.8191249370575</v>
+        <v>158.457043170929</v>
       </c>
       <c r="D3" t="n">
         <v>8.909999847412109</v>
       </c>
       <c r="E3" t="n">
-        <v>0.324638976862556</v>
+        <v>0.3345538234481445</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1556092351675033</v>
+        <v>0.2964028418064117</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1608882248401641</v>
+        <v>0.319589227437973</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1606370061635971</v>
+        <v>0.319499522447586</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1166812181472778</v>
+        <v>0.103586308658123</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1188521832227706</v>
+        <v>0.1249542906880378</v>
       </c>
       <c r="K3" t="n">
-        <v>346.599684715271</v>
+        <v>377.5164985656738</v>
       </c>
       <c r="L3" t="n">
-        <v>2.365500450134277</v>
+        <v>2.760414838790894</v>
       </c>
       <c r="M3" t="n">
-        <v>13.03968691825867</v>
+        <v>12.86736965179443</v>
       </c>
       <c r="N3" t="n">
-        <v>21.59745907783508</v>
+        <v>22.63592147827148</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0788500150044759</v>
+        <v>0.0920138279596964</v>
       </c>
       <c r="P3" t="n">
-        <v>0.4346562306086222</v>
+        <v>0.4289123217264811</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.7199153025945028</v>
+        <v>0.7545307159423829</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250630-190805</t>
+          <t>20250718-212718</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -3099,22 +3099,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -3124,10 +3124,10 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -3146,56 +3146,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="C4" t="n">
-        <v>60.10979080200195</v>
+        <v>111.1485781669617</v>
       </c>
       <c r="D4" t="n">
         <v>8.909999847412109</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3259112583963494</v>
+        <v>0.3361198074287838</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1736536622047424</v>
+        <v>0.2190846502780914</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1811102628707885</v>
+        <v>0.2217263877391815</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1807821393013</v>
+        <v>0.2216576933860778</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0948203578591346</v>
+        <v>0.0585801266133785</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1153600364923477</v>
+        <v>0.1168950051069259</v>
       </c>
       <c r="K4" t="n">
-        <v>346.9709231853485</v>
+        <v>349.7344937324524</v>
       </c>
       <c r="L4" t="n">
-        <v>2.345439195632935</v>
+        <v>2.688814878463745</v>
       </c>
       <c r="M4" t="n">
-        <v>13.11596965789795</v>
+        <v>12.73774838447571</v>
       </c>
       <c r="N4" t="n">
-        <v>21.9350643157959</v>
+        <v>20.79278779029847</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0781813065210978</v>
+        <v>0.0896271626154581</v>
       </c>
       <c r="P4" t="n">
-        <v>0.4371989885965983</v>
+        <v>0.4245916128158569</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.7311688105265299</v>
+        <v>0.693092926343282</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250630-191638</t>
+          <t>20250718-213807</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -3220,22 +3220,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -3245,10 +3245,10 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -3267,56 +3267,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>19</v>
+        <v>52</v>
       </c>
       <c r="C5" t="n">
-        <v>60.08629179000855</v>
+        <v>156.7468240261078</v>
       </c>
       <c r="D5" t="n">
         <v>8.909999847412109</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3294356575137691</v>
+        <v>0.3301479913867436</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1795949637889862</v>
+        <v>0.2738633453845978</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1792797446250915</v>
+        <v>0.2883166670799255</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1791229397058487</v>
+        <v>0.2876529991626739</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1376138031482696</v>
+        <v>0.1653838753700256</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1226145252585411</v>
+        <v>0.1132382377982139</v>
       </c>
       <c r="K5" t="n">
-        <v>345.4120693206787</v>
+        <v>350.0843920707703</v>
       </c>
       <c r="L5" t="n">
-        <v>2.366075277328491</v>
+        <v>2.777834415435791</v>
       </c>
       <c r="M5" t="n">
-        <v>13.19029498100281</v>
+        <v>13.46274256706238</v>
       </c>
       <c r="N5" t="n">
-        <v>21.50027132034302</v>
+        <v>21.08265447616577</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0788691759109497</v>
+        <v>0.0925944805145263</v>
       </c>
       <c r="P5" t="n">
-        <v>0.4396764993667602</v>
+        <v>0.4487580855687459</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.7166757106781005</v>
+        <v>0.7027551492055257</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250630-192513</t>
+          <t>20250718-214744</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -3341,22 +3341,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -3366,10 +3366,10 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -3379,7 +3379,7 @@
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -3388,56 +3388,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C6" t="n">
-        <v>59.78960204124451</v>
+        <v>74.70913982391357</v>
       </c>
       <c r="D6" t="n">
         <v>8.909999847412109</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3233590627971448</v>
+        <v>0.328757689644893</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1795718371868133</v>
+        <v>0.1811384111642837</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1874089837074279</v>
+        <v>0.1817440390586853</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1873162239789962</v>
+        <v>0.1815578043460846</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1149570569396019</v>
+        <v>0.1168839856982231</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1175653263926506</v>
+        <v>0.1119240149855613</v>
       </c>
       <c r="K6" t="n">
-        <v>345.2779669761658</v>
+        <v>349.8526771068573</v>
       </c>
       <c r="L6" t="n">
-        <v>2.358654022216797</v>
+        <v>2.693390607833862</v>
       </c>
       <c r="M6" t="n">
-        <v>13.06697630882263</v>
+        <v>13.06260204315186</v>
       </c>
       <c r="N6" t="n">
-        <v>22.05898308753968</v>
+        <v>20.70151233673096</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0786218007405599</v>
+        <v>0.08977968692779539</v>
       </c>
       <c r="P6" t="n">
-        <v>0.4355658769607544</v>
+        <v>0.4354200681050618</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.7352994362513224</v>
+        <v>0.6900504112243653</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250630-193346</t>
+          <t>20250718-215806</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -3462,22 +3462,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -3487,10 +3487,10 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -3500,7 +3500,7 @@
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -3675,56 +3675,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>19</v>
+        <v>60</v>
       </c>
       <c r="C2" t="n">
-        <v>45.1331160068512</v>
+        <v>130.5854578018188</v>
       </c>
       <c r="D2" t="n">
-        <v>7.769999980926514</v>
+        <v>7.78000020980835</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2006509249147615</v>
+        <v>0.1990370931724707</v>
       </c>
       <c r="F2" t="n">
-        <v>0.09711919724941249</v>
+        <v>0.2517269551753998</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1050454974174499</v>
+        <v>0.261653184890747</v>
       </c>
       <c r="H2" t="n">
-        <v>0.105005569756031</v>
+        <v>0.2616105675697326</v>
       </c>
       <c r="I2" t="n">
-        <v>0.09617962688207619</v>
+        <v>0.2272599637508392</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0843555778264999</v>
+        <v>0.0838040634989738</v>
       </c>
       <c r="K2" t="n">
-        <v>54.87773966789246</v>
+        <v>48.14171886444092</v>
       </c>
       <c r="L2" t="n">
-        <v>2.013832807540894</v>
+        <v>2.002895355224609</v>
       </c>
       <c r="M2" t="n">
-        <v>10.14797496795654</v>
+        <v>10.80359601974487</v>
       </c>
       <c r="N2" t="n">
-        <v>11.99608874320984</v>
+        <v>12.47163772583008</v>
       </c>
       <c r="O2" t="n">
-        <v>0.06712776025136311</v>
+        <v>0.06676317850748691</v>
       </c>
       <c r="P2" t="n">
-        <v>0.3382658322652181</v>
+        <v>0.3601198673248291</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.3998696247736613</v>
+        <v>0.4157212575276692</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250701-051511</t>
+          <t>20250719-133842</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -3749,22 +3749,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -3774,10 +3774,10 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -3787,7 +3787,7 @@
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -3796,56 +3796,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19</v>
+        <v>56</v>
       </c>
       <c r="C3" t="n">
-        <v>44.82975578308105</v>
+        <v>121.9080450534821</v>
       </c>
       <c r="D3" t="n">
         <v>7.769999980926514</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1985549001317274</v>
+        <v>0.198766111263207</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1135751754045486</v>
+        <v>0.2848607301712036</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1210118755698204</v>
+        <v>0.2877472937107086</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1209233105182647</v>
+        <v>0.2879523038864136</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1165816336870193</v>
+        <v>0.26792773604393</v>
       </c>
       <c r="J3" t="n">
-        <v>0.08465180546045301</v>
+        <v>0.08587080985307689</v>
       </c>
       <c r="K3" t="n">
-        <v>55.36741161346436</v>
+        <v>42.3604793548584</v>
       </c>
       <c r="L3" t="n">
-        <v>1.997539758682251</v>
+        <v>1.955503463745117</v>
       </c>
       <c r="M3" t="n">
-        <v>9.50036096572876</v>
+        <v>10.43646502494812</v>
       </c>
       <c r="N3" t="n">
-        <v>14.17714405059814</v>
+        <v>11.91979598999023</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0665846586227417</v>
+        <v>0.0651834487915039</v>
       </c>
       <c r="P3" t="n">
-        <v>0.3166786988576253</v>
+        <v>0.3478821674982706</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.4725714683532714</v>
+        <v>0.3973265329996744</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250701-051816</t>
+          <t>20250719-134308</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -3870,22 +3870,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -3895,10 +3895,10 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -3917,56 +3917,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>19</v>
+        <v>84</v>
       </c>
       <c r="C4" t="n">
-        <v>45.38452529907227</v>
+        <v>181.0660026073456</v>
       </c>
       <c r="D4" t="n">
         <v>7.769999980926514</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1989767559264835</v>
+        <v>0.1981565125641368</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1146394237875938</v>
+        <v>0.416887491941452</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1197163090109825</v>
+        <v>0.4222943782806396</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1196264028549194</v>
+        <v>0.421707808971405</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1157938167452812</v>
+        <v>0.4191970229148865</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0848817005753517</v>
+        <v>0.0848196372389793</v>
       </c>
       <c r="K4" t="n">
-        <v>52.61965942382812</v>
+        <v>42.07991600036621</v>
       </c>
       <c r="L4" t="n">
-        <v>2.005552530288696</v>
+        <v>2.06041145324707</v>
       </c>
       <c r="M4" t="n">
-        <v>9.324581384658812</v>
+        <v>10.17653346061706</v>
       </c>
       <c r="N4" t="n">
-        <v>13.16351175308228</v>
+        <v>12.75722932815552</v>
       </c>
       <c r="O4" t="n">
-        <v>0.06685175100962321</v>
+        <v>0.06868038177490229</v>
       </c>
       <c r="P4" t="n">
-        <v>0.3108193794886271</v>
+        <v>0.3392177820205688</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.4387837251027425</v>
+        <v>0.4252409776051839</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250701-052123</t>
+          <t>20250719-134724</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -3991,22 +3991,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -4016,10 +4016,10 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -4029,7 +4029,7 @@
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -4038,56 +4038,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="C5" t="n">
-        <v>45.15139818191528</v>
+        <v>88.22235488891602</v>
       </c>
       <c r="D5" t="n">
         <v>7.769999980926514</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1984918360647402</v>
+        <v>0.1988526985049247</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1132591217756271</v>
+        <v>0.1719351261854171</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1188815087080001</v>
+        <v>0.1817498505115509</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1188028156757354</v>
+        <v>0.1816181093454361</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1205492615699768</v>
+        <v>0.1674363911151886</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0832169726490974</v>
+        <v>0.0848665088415145</v>
       </c>
       <c r="K5" t="n">
-        <v>47.43651366233826</v>
+        <v>48.35477375984192</v>
       </c>
       <c r="L5" t="n">
-        <v>2.327792406082153</v>
+        <v>2.019634246826172</v>
       </c>
       <c r="M5" t="n">
-        <v>9.442374467849731</v>
+        <v>10.55477476119995</v>
       </c>
       <c r="N5" t="n">
-        <v>13.30264544487</v>
+        <v>11.7294774055481</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0775930802027384</v>
+        <v>0.06732114156087229</v>
       </c>
       <c r="P5" t="n">
-        <v>0.314745815594991</v>
+        <v>0.3518258253733317</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.4434215148289998</v>
+        <v>0.3909825801849365</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250701-052426</t>
+          <t>20250719-135240</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -4112,22 +4112,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -4137,10 +4137,10 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -4150,7 +4150,7 @@
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -4159,56 +4159,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>19</v>
+        <v>72</v>
       </c>
       <c r="C6" t="n">
-        <v>45.43489933013916</v>
+        <v>156.397878408432</v>
       </c>
       <c r="D6" t="n">
         <v>7.769999980926514</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2018209319365651</v>
+        <v>0.19890750799742</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1127660274505615</v>
+        <v>0.3612143993377685</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1199914142489433</v>
+        <v>0.3658285140991211</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1200247481465339</v>
+        <v>0.3656815886497497</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1177931725978851</v>
+        <v>0.3463213443756103</v>
       </c>
       <c r="J6" t="n">
-        <v>0.08250013738870619</v>
+        <v>0.0831448212265968</v>
       </c>
       <c r="K6" t="n">
-        <v>48.91222405433655</v>
+        <v>48.20614147186279</v>
       </c>
       <c r="L6" t="n">
-        <v>1.991720914840698</v>
+        <v>2.352224588394165</v>
       </c>
       <c r="M6" t="n">
-        <v>9.327427864074709</v>
+        <v>10.3447048664093</v>
       </c>
       <c r="N6" t="n">
-        <v>15.95758128166199</v>
+        <v>12.02212619781494</v>
       </c>
       <c r="O6" t="n">
-        <v>0.06639069716135659</v>
+        <v>0.0784074862798055</v>
       </c>
       <c r="P6" t="n">
-        <v>0.3109142621358235</v>
+        <v>0.3448234955469767</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.5319193760553996</v>
+        <v>0.4007375399271647</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250701-052725</t>
+          <t>20250719-135622</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -4233,22 +4233,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -4258,10 +4258,10 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -4271,7 +4271,7 @@
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -4446,56 +4446,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>19</v>
+        <v>52</v>
       </c>
       <c r="C2" t="n">
-        <v>29.7462055683136</v>
+        <v>76.01842427253723</v>
       </c>
       <c r="D2" t="n">
-        <v>4.670000076293945</v>
+        <v>4.659999847412109</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1181449811709554</v>
+        <v>0.1188945221499754</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1081196218729019</v>
+        <v>0.1599507480859756</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1153493896126747</v>
+        <v>0.1625731140375137</v>
       </c>
       <c r="H2" t="n">
-        <v>0.115455612540245</v>
+        <v>0.1623952090740203</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1128642559051513</v>
+        <v>0.1627833098173141</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0604865215718746</v>
+        <v>0.061225701123476</v>
       </c>
       <c r="K2" t="n">
-        <v>25.2445764541626</v>
+        <v>30.05169463157653</v>
       </c>
       <c r="L2" t="n">
-        <v>1.420362234115601</v>
+        <v>1.386127710342407</v>
       </c>
       <c r="M2" t="n">
-        <v>9.039480447769163</v>
+        <v>8.008608818054199</v>
       </c>
       <c r="N2" t="n">
-        <v>14.97552347183228</v>
+        <v>9.229219436645508</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0473454078038533</v>
+        <v>0.0462042570114135</v>
       </c>
       <c r="P2" t="n">
-        <v>0.3013160149256388</v>
+        <v>0.2669536272684733</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.4991841157277425</v>
+        <v>0.3076406478881835</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250701-080939</t>
+          <t>20250719-200203</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -4520,22 +4520,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -4545,10 +4545,10 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -4558,7 +4558,7 @@
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -4567,56 +4567,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="C3" t="n">
-        <v>29.71529746055603</v>
+        <v>48.88620281219482</v>
       </c>
       <c r="D3" t="n">
-        <v>4.659999847412109</v>
+        <v>4.670000076293945</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1193084591313412</v>
+        <v>0.1193703850731253</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1125521063804626</v>
+        <v>0.1342638731002807</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1179625988006591</v>
+        <v>0.1427924335002899</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1180434077978134</v>
+        <v>0.1426872760057449</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1189747005701065</v>
+        <v>0.1450531780719757</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0609407424926757</v>
+        <v>0.059993028640747</v>
       </c>
       <c r="K3" t="n">
-        <v>32.04050779342651</v>
+        <v>24.96024608612061</v>
       </c>
       <c r="L3" t="n">
-        <v>1.3650062084198</v>
+        <v>1.656467437744141</v>
       </c>
       <c r="M3" t="n">
-        <v>9.04361057281494</v>
+        <v>8.685084104537964</v>
       </c>
       <c r="N3" t="n">
-        <v>17.28519821166992</v>
+        <v>9.083806753158569</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0455002069473266</v>
+        <v>0.055215581258138</v>
       </c>
       <c r="P3" t="n">
-        <v>0.301453685760498</v>
+        <v>0.2895028034845988</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.5761732737223307</v>
+        <v>0.302793558438619</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250701-081157</t>
+          <t>20250719-200501</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -4641,22 +4641,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -4666,10 +4666,10 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -4679,7 +4679,7 @@
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -4688,56 +4688,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>19</v>
+        <v>56</v>
       </c>
       <c r="C4" t="n">
-        <v>29.44217276573181</v>
+        <v>82.21870684623718</v>
       </c>
       <c r="D4" t="n">
-        <v>4.659999847412109</v>
+        <v>4.670000076293945</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1189566736942843</v>
+        <v>0.1199040306465965</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1152707859873771</v>
+        <v>0.1689963042736053</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1193072795867919</v>
+        <v>0.1883372515439987</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1192016303539276</v>
+        <v>0.1887300163507461</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1153915673494339</v>
+        <v>0.1873496174812317</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0616349689662456</v>
+        <v>0.0608474239706993</v>
       </c>
       <c r="K4" t="n">
-        <v>26.18455743789673</v>
+        <v>29.85995316505432</v>
       </c>
       <c r="L4" t="n">
-        <v>1.635236263275146</v>
+        <v>1.382637739181519</v>
       </c>
       <c r="M4" t="n">
-        <v>9.126355171203612</v>
+        <v>8.504799604415894</v>
       </c>
       <c r="N4" t="n">
-        <v>19.92897367477417</v>
+        <v>10.0040340423584</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0545078754425048</v>
+        <v>0.0460879246393839</v>
       </c>
       <c r="P4" t="n">
-        <v>0.3042118390401204</v>
+        <v>0.2834933201471964</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.6642991224924724</v>
+        <v>0.3334678014119466</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250701-081418</t>
+          <t>20250719-200732</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -4762,22 +4762,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -4787,10 +4787,10 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -4800,7 +4800,7 @@
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -4809,56 +4809,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="C5" t="n">
-        <v>29.65583801269531</v>
+        <v>71.23527598381042</v>
       </c>
       <c r="D5" t="n">
-        <v>4.670000076293945</v>
+        <v>4.659999847412109</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1202165190326539</v>
+        <v>0.1191580719314515</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0992099866271019</v>
+        <v>0.1634296327829361</v>
       </c>
       <c r="G5" t="n">
-        <v>0.106284812092781</v>
+        <v>0.1686016470193863</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1064136773347854</v>
+        <v>0.1686245799064636</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1074916645884513</v>
+        <v>0.1695459336042404</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0600466579198837</v>
+        <v>0.0605977997183799</v>
       </c>
       <c r="K5" t="n">
-        <v>24.22031426429749</v>
+        <v>29.97423362731934</v>
       </c>
       <c r="L5" t="n">
-        <v>1.629408121109009</v>
+        <v>1.44914436340332</v>
       </c>
       <c r="M5" t="n">
-        <v>9.2212975025177</v>
+        <v>8.003356456756592</v>
       </c>
       <c r="N5" t="n">
-        <v>26.00811982154847</v>
+        <v>9.453309535980225</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0543136040369669</v>
+        <v>0.048304812113444</v>
       </c>
       <c r="P5" t="n">
-        <v>0.3073765834172566</v>
+        <v>0.266778548558553</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.8669373273849488</v>
+        <v>0.3151103178660074</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250701-081642</t>
+          <t>20250719-201018</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -4883,22 +4883,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -4908,10 +4908,10 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -4921,7 +4921,7 @@
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -4930,56 +4930,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="C6" t="n">
-        <v>29.77881765365601</v>
+        <v>43.30517172813416</v>
       </c>
       <c r="D6" t="n">
         <v>4.659999847412109</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1191191390941017</v>
+        <v>0.1194496694952249</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1067054197192192</v>
+        <v>0.1144793182611465</v>
       </c>
       <c r="G6" t="n">
-        <v>0.114067830145359</v>
+        <v>0.1210009157657623</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1141039803624153</v>
+        <v>0.1210547313094139</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1093985065817833</v>
+        <v>0.1205882802605629</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0601296424865722</v>
+        <v>0.0633328929543495</v>
       </c>
       <c r="K6" t="n">
-        <v>24.1819281578064</v>
+        <v>24.50400424003601</v>
       </c>
       <c r="L6" t="n">
-        <v>1.409987449645996</v>
+        <v>1.700155019760132</v>
       </c>
       <c r="M6" t="n">
-        <v>9.313622713088989</v>
+        <v>8.279247522354126</v>
       </c>
       <c r="N6" t="n">
-        <v>28.7647533416748</v>
+        <v>9.620832681655884</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0469995816548665</v>
+        <v>0.0566718339920043</v>
       </c>
       <c r="P6" t="n">
-        <v>0.3104540904362996</v>
+        <v>0.2759749174118042</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.9588251113891602</v>
+        <v>0.3206944227218627</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250701-081911</t>
+          <t>20250719-201311</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -5004,22 +5004,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -5029,10 +5029,10 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -5042,7 +5042,7 @@
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -5217,56 +5217,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C2" t="n">
-        <v>25.8605945110321</v>
+        <v>27.41730213165283</v>
       </c>
       <c r="D2" t="n">
         <v>3.509999990463257</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1019697655972681</v>
+        <v>0.1051087640225886</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0905995666980743</v>
+        <v>0.0597583651542663</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0946602076292038</v>
+        <v>0.0610887594521045</v>
       </c>
       <c r="H2" t="n">
-        <v>0.094615951180458</v>
+        <v>0.0609752684831619</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0253931004554033</v>
+        <v>0.0604841113090515</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0513334758579731</v>
+        <v>0.0533258132636547</v>
       </c>
       <c r="K2" t="n">
-        <v>26.23436260223389</v>
+        <v>26.83817148208618</v>
       </c>
       <c r="L2" t="n">
-        <v>1.564987659454346</v>
+        <v>1.313525438308716</v>
       </c>
       <c r="M2" t="n">
-        <v>8.120753526687622</v>
+        <v>8.775502920150757</v>
       </c>
       <c r="N2" t="n">
-        <v>9.719464540481567</v>
+        <v>9.85105562210083</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0521662553151448</v>
+        <v>0.0437841812769571</v>
       </c>
       <c r="P2" t="n">
-        <v>0.2706917842229207</v>
+        <v>0.2925167640050252</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.3239821513493855</v>
+        <v>0.3283685207366943</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250701-101921</t>
+          <t>20250720-002434</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -5291,22 +5291,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -5316,10 +5316,10 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -5329,7 +5329,7 @@
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -5338,56 +5338,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19</v>
+        <v>72</v>
       </c>
       <c r="C3" t="n">
-        <v>25.6339077949524</v>
+        <v>91.27635478973389</v>
       </c>
       <c r="D3" t="n">
         <v>3.509999990463257</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1042716848222832</v>
+        <v>0.1066085601018534</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1034760326147079</v>
+        <v>0.1605273187160492</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1105940192937851</v>
+        <v>0.1665329486131668</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1106012836098671</v>
+        <v>0.1667248755693435</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1117465272545814</v>
+        <v>0.1659938693046569</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0556384734809398</v>
+        <v>0.0521037727594375</v>
       </c>
       <c r="K3" t="n">
-        <v>26.24453544616699</v>
+        <v>21.38771510124207</v>
       </c>
       <c r="L3" t="n">
-        <v>1.22249436378479</v>
+        <v>1.319232702255249</v>
       </c>
       <c r="M3" t="n">
-        <v>8.07030177116394</v>
+        <v>8.167494058609009</v>
       </c>
       <c r="N3" t="n">
-        <v>9.225574731826782</v>
+        <v>10.40548133850098</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0407498121261596</v>
+        <v>0.0439744234085083</v>
       </c>
       <c r="P3" t="n">
-        <v>0.269010059038798</v>
+        <v>0.2722498019536336</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.3075191577275594</v>
+        <v>0.3468493779500325</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250701-102124</t>
+          <t>20250720-002642</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -5412,22 +5412,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -5437,10 +5437,10 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -5450,7 +5450,7 @@
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -5459,56 +5459,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="C4" t="n">
-        <v>25.63681268692017</v>
+        <v>51.20920085906982</v>
       </c>
       <c r="D4" t="n">
         <v>3.509999990463257</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1033170140887561</v>
+        <v>0.1043710872530936</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0776412859559059</v>
+        <v>0.1160942018032074</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0810047313570976</v>
+        <v>0.1215138584375381</v>
       </c>
       <c r="H4" t="n">
-        <v>0.08108086138963699</v>
+        <v>0.1214422881603241</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0846079066395759</v>
+        <v>0.1224136501550674</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0543718002736568</v>
+        <v>0.0528568252921104</v>
       </c>
       <c r="K4" t="n">
-        <v>26.11892700195312</v>
+        <v>26.62878060340881</v>
       </c>
       <c r="L4" t="n">
-        <v>1.558861255645752</v>
+        <v>1.276059865951538</v>
       </c>
       <c r="M4" t="n">
-        <v>7.994752407073975</v>
+        <v>8.045118808746338</v>
       </c>
       <c r="N4" t="n">
-        <v>10.15817308425903</v>
+        <v>9.876879453659058</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0519620418548584</v>
+        <v>0.0425353288650512</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2664917469024658</v>
+        <v>0.2681706269582112</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.3386057694753011</v>
+        <v>0.3292293151219685</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250701-102327</t>
+          <t>20250720-002934</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -5533,22 +5533,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -5558,10 +5558,10 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -5571,7 +5571,7 @@
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -5580,56 +5580,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C5" t="n">
-        <v>25.89408254623413</v>
+        <v>27.74294757843018</v>
       </c>
       <c r="D5" t="n">
         <v>3.509999990463257</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1029760500318125</v>
+        <v>0.1047015648335218</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1177453249692916</v>
+        <v>0.0759712308645248</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1202982515096664</v>
+        <v>0.0833161994814872</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1201391965150833</v>
+        <v>0.0832781195640564</v>
       </c>
       <c r="I5" t="n">
-        <v>0.118815392255783</v>
+        <v>0.083495020866394</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0513322502374649</v>
+        <v>0.0515838451683521</v>
       </c>
       <c r="K5" t="n">
-        <v>26.02521276473999</v>
+        <v>26.70889115333557</v>
       </c>
       <c r="L5" t="n">
-        <v>1.510485887527466</v>
+        <v>1.591989040374756</v>
       </c>
       <c r="M5" t="n">
-        <v>7.846790075302124</v>
+        <v>8.635213136672974</v>
       </c>
       <c r="N5" t="n">
-        <v>9.638674736022949</v>
+        <v>9.812734127044678</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0503495295842488</v>
+        <v>0.0530663013458252</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2615596691767374</v>
+        <v>0.2878404378890991</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.3212891578674316</v>
+        <v>0.3270911375681559</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250701-102531</t>
+          <t>20250720-003206</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -5654,22 +5654,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -5679,10 +5679,10 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -5692,7 +5692,7 @@
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -5701,56 +5701,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="C6" t="n">
-        <v>25.72727513313293</v>
+        <v>46.58230495452881</v>
       </c>
       <c r="D6" t="n">
         <v>3.509999990463257</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1037826483186922</v>
+        <v>0.1039475471609168</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0604074597358703</v>
+        <v>0.1180523186922073</v>
       </c>
       <c r="G6" t="n">
-        <v>0.06387089192867269</v>
+        <v>0.1227759569883346</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0640523210167884</v>
+        <v>0.1224845722317695</v>
       </c>
       <c r="I6" t="n">
-        <v>0.06270457804203031</v>
+        <v>0.1220573410391807</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0531864650547504</v>
+        <v>0.0516644157469272</v>
       </c>
       <c r="K6" t="n">
-        <v>26.33393287658692</v>
+        <v>26.81454372406006</v>
       </c>
       <c r="L6" t="n">
-        <v>1.258527517318726</v>
+        <v>1.277306318283081</v>
       </c>
       <c r="M6" t="n">
-        <v>8.078869819641113</v>
+        <v>8.147143125534058</v>
       </c>
       <c r="N6" t="n">
-        <v>9.528723478317261</v>
+        <v>9.645028352737429</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0419509172439575</v>
+        <v>0.0425768772761027</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2692956606547038</v>
+        <v>0.2715714375178019</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.3176241159439087</v>
+        <v>0.3215009450912475</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250701-102734</t>
+          <t>20250720-003414</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -5775,22 +5775,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -5800,10 +5800,10 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -5813,7 +5813,7 @@
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>

--- a/tests/perf_v2/perf_history/v2.5/semantic_segmentation/SEMANTIC_SEGMENTATION-raw-small_aerial.xlsx
+++ b/tests/perf_v2/perf_history/v2.5/semantic_segmentation/SEMANTIC_SEGMENTATION-raw-small_aerial.xlsx
@@ -591,56 +591,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>24</v>
+        <v>83</v>
       </c>
       <c r="C2" t="n">
-        <v>24.20329546928406</v>
+        <v>74.03155446052551</v>
       </c>
       <c r="D2" t="n">
-        <v>1.159999966621399</v>
+        <v>1.169999957084656</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0562944149908919</v>
+        <v>0.0564529161945164</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5385844707489014</v>
+        <v>0.5591782927513123</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5363255739212036</v>
+        <v>0.5608916282653809</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5365433692932129</v>
+        <v>0.5601013898849487</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5355786085128784</v>
+        <v>0.5611768960952759</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0424073226749897</v>
+        <v>0.0441626869142055</v>
       </c>
       <c r="K2" t="n">
-        <v>30.9040105342865</v>
+        <v>30.74131441116333</v>
       </c>
       <c r="L2" t="n">
-        <v>1.185202360153198</v>
+        <v>1.219282627105713</v>
       </c>
       <c r="M2" t="n">
-        <v>8.66538143157959</v>
+        <v>8.581675052642822</v>
       </c>
       <c r="N2" t="n">
-        <v>9.642174482345579</v>
+        <v>8.614063501358032</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0395067453384399</v>
+        <v>0.0406427542368571</v>
       </c>
       <c r="P2" t="n">
-        <v>0.2888460477193196</v>
+        <v>0.286055835088094</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.321405816078186</v>
+        <v>0.2871354500452677</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250720-050116</t>
+          <t>20250723-154457</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -712,56 +712,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="C3" t="n">
-        <v>23.73980832099915</v>
+        <v>60.37949228286743</v>
       </c>
       <c r="D3" t="n">
         <v>1.169999957084656</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0554243647493421</v>
+        <v>0.0569829941907925</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5237066149711609</v>
+        <v>0.5614606142044067</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5276978015899658</v>
+        <v>0.5595908164978027</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5273638367652893</v>
+        <v>0.5591869354248047</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5271754264831543</v>
+        <v>0.5588924884796143</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0418689399957656</v>
+        <v>0.0408208705484867</v>
       </c>
       <c r="K3" t="n">
-        <v>30.8991858959198</v>
+        <v>30.31975269317627</v>
       </c>
       <c r="L3" t="n">
-        <v>1.194629669189453</v>
+        <v>1.298566102981567</v>
       </c>
       <c r="M3" t="n">
-        <v>8.759116649627686</v>
+        <v>8.525238990783691</v>
       </c>
       <c r="N3" t="n">
-        <v>9.355445146560667</v>
+        <v>9.525456666946411</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0398209889729817</v>
+        <v>0.0432855367660522</v>
       </c>
       <c r="P3" t="n">
-        <v>0.2919705549875895</v>
+        <v>0.284174633026123</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.3118481715520223</v>
+        <v>0.317515222231547</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250720-050322</t>
+          <t>20250723-154751</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -833,56 +833,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>19</v>
+        <v>59</v>
       </c>
       <c r="C4" t="n">
-        <v>19.5289077758789</v>
+        <v>53.25890803337097</v>
       </c>
       <c r="D4" t="n">
         <v>1.159999966621399</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0561105559923146</v>
+        <v>0.0568946630267773</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5217826366424561</v>
+        <v>0.5534349679946899</v>
       </c>
       <c r="G4" t="n">
-        <v>0.523837149143219</v>
+        <v>0.550782322883606</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5236536860466003</v>
+        <v>0.5502772331237793</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5219542384147644</v>
+        <v>0.551174521446228</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0440789237618446</v>
+        <v>0.0435892418026924</v>
       </c>
       <c r="K4" t="n">
-        <v>30.65856432914734</v>
+        <v>30.62128806114197</v>
       </c>
       <c r="L4" t="n">
-        <v>1.250608444213867</v>
+        <v>1.189301490783691</v>
       </c>
       <c r="M4" t="n">
-        <v>8.738326072692871</v>
+        <v>8.461563348770142</v>
       </c>
       <c r="N4" t="n">
-        <v>9.201722621917725</v>
+        <v>8.612008094787598</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0416869481404622</v>
+        <v>0.039643383026123</v>
       </c>
       <c r="P4" t="n">
-        <v>0.291277535756429</v>
+        <v>0.2820521116256714</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.3067240873972575</v>
+        <v>0.2870669364929199</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250720-050526</t>
+          <t>20250723-155032</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -954,56 +954,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>19</v>
+        <v>63</v>
       </c>
       <c r="C5" t="n">
-        <v>19.61807084083557</v>
+        <v>56.27069640159607</v>
       </c>
       <c r="D5" t="n">
-        <v>1.159999966621399</v>
+        <v>1.179999947547913</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0559926191835026</v>
+        <v>0.0570179662770694</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5383193492889404</v>
+        <v>0.5673131346702576</v>
       </c>
       <c r="G5" t="n">
-        <v>0.539786696434021</v>
+        <v>0.5663585662841797</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5400868058204651</v>
+        <v>0.5661864280700684</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5393303632736206</v>
+        <v>0.5650627017021179</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0440717861056327</v>
+        <v>0.0428553894162178</v>
       </c>
       <c r="K5" t="n">
-        <v>30.86731338500977</v>
+        <v>30.47654128074646</v>
       </c>
       <c r="L5" t="n">
-        <v>1.24501895904541</v>
+        <v>1.201112508773804</v>
       </c>
       <c r="M5" t="n">
-        <v>8.823449850082397</v>
+        <v>8.524959564208984</v>
       </c>
       <c r="N5" t="n">
-        <v>9.043648242950439</v>
+        <v>9.113078594207764</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0415006319681803</v>
+        <v>0.0400370836257934</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2941149950027465</v>
+        <v>0.2841653188069661</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.3014549414316813</v>
+        <v>0.3037692864735921</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250720-050727</t>
+          <t>20250723-155304</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1075,56 +1075,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>36</v>
+        <v>95</v>
       </c>
       <c r="C6" t="n">
-        <v>35.29046177864075</v>
+        <v>84.20652270317078</v>
       </c>
       <c r="D6" t="n">
-        <v>1.360000014305115</v>
+        <v>1.169999957084656</v>
       </c>
       <c r="E6" t="n">
-        <v>0.056716166022751</v>
+        <v>0.0568378478680785</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5454379320144653</v>
+        <v>0.5678078532218933</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5506823658943176</v>
+        <v>0.567898154258728</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5506055951118469</v>
+        <v>0.567400336265564</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5491693019866943</v>
+        <v>0.5665112137794495</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0414758846163749</v>
+        <v>0.0432341881096363</v>
       </c>
       <c r="K6" t="n">
-        <v>30.85289001464844</v>
+        <v>30.62247753143311</v>
       </c>
       <c r="L6" t="n">
-        <v>1.217617750167847</v>
+        <v>1.284454345703125</v>
       </c>
       <c r="M6" t="n">
-        <v>8.998705387115479</v>
+        <v>8.44351601600647</v>
       </c>
       <c r="N6" t="n">
-        <v>9.269238710403442</v>
+        <v>9.001266956329346</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0405872583389282</v>
+        <v>0.0428151448567708</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2999568462371826</v>
+        <v>0.2814505338668823</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.3089746236801147</v>
+        <v>0.3000422318776448</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250720-050927</t>
+          <t>20250723-155541</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1362,56 +1362,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>68</v>
+        <v>107</v>
       </c>
       <c r="C2" t="n">
-        <v>111.1647372245789</v>
+        <v>170.2831938266754</v>
       </c>
       <c r="D2" t="n">
-        <v>3.059999942779541</v>
+        <v>3.009999990463257</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1528739098678616</v>
+        <v>0.1484836260570543</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3940041065216064</v>
+        <v>0.4272022247314453</v>
       </c>
       <c r="G2" t="n">
-        <v>0.40372234582901</v>
+        <v>0.437467873096466</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4021303355693817</v>
+        <v>0.437564492225647</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3905501961708069</v>
+        <v>0.4325957894325256</v>
       </c>
       <c r="J2" t="n">
-        <v>0.077861376106739</v>
+        <v>0.0778537616133689</v>
       </c>
       <c r="K2" t="n">
-        <v>68.02818703651428</v>
+        <v>67.30943059921265</v>
       </c>
       <c r="L2" t="n">
-        <v>1.6501784324646</v>
+        <v>1.656048059463501</v>
       </c>
       <c r="M2" t="n">
-        <v>9.393870830535889</v>
+        <v>9.932249069213867</v>
       </c>
       <c r="N2" t="n">
-        <v>11.79795479774475</v>
+        <v>12.26728844642639</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0550059477488199</v>
+        <v>0.0552016019821166</v>
       </c>
       <c r="P2" t="n">
-        <v>0.3131290276845296</v>
+        <v>0.3310749689737955</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.393265159924825</v>
+        <v>0.4089096148808797</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250718-085434</t>
+          <t>20250721-142924</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -1483,56 +1483,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>44</v>
+        <v>127</v>
       </c>
       <c r="C3" t="n">
-        <v>73.73867893218994</v>
+        <v>201.5488719940185</v>
       </c>
       <c r="D3" t="n">
-        <v>3.059999942779541</v>
+        <v>3.009999990463257</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1517002006823365</v>
+        <v>0.1502328653504529</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2837473154067993</v>
+        <v>0.432689756155014</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2961084246635437</v>
+        <v>0.4436940252780914</v>
       </c>
       <c r="H3" t="n">
-        <v>0.295762687921524</v>
+        <v>0.4427821636199951</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2920447289943695</v>
+        <v>0.4360827505588531</v>
       </c>
       <c r="J3" t="n">
-        <v>0.07283768802881239</v>
+        <v>0.0729022324085235</v>
       </c>
       <c r="K3" t="n">
-        <v>61.34244108200073</v>
+        <v>67.41804885864258</v>
       </c>
       <c r="L3" t="n">
-        <v>1.640236616134644</v>
+        <v>1.988246917724609</v>
       </c>
       <c r="M3" t="n">
-        <v>9.05840229988098</v>
+        <v>9.310141801834106</v>
       </c>
       <c r="N3" t="n">
-        <v>11.21808004379272</v>
+        <v>11.10334801673889</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0546745538711547</v>
+        <v>0.06627489725748691</v>
       </c>
       <c r="P3" t="n">
-        <v>0.301946743329366</v>
+        <v>0.3103380600611369</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.3739360014597574</v>
+        <v>0.370111600557963</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250718-085841</t>
+          <t>20250721-143451</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -1604,56 +1604,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32</v>
+        <v>115</v>
       </c>
       <c r="C4" t="n">
-        <v>54.31889677047729</v>
+        <v>183.8270118236541</v>
       </c>
       <c r="D4" t="n">
-        <v>3.059999942779541</v>
+        <v>3.009999990463257</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1504291528835892</v>
+        <v>0.1509774566992469</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2240137159824371</v>
+        <v>0.4537617564201355</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2340574860572815</v>
+        <v>0.4563308358192444</v>
       </c>
       <c r="H4" t="n">
-        <v>0.234003409743309</v>
+        <v>0.4560153484344482</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2341594845056533</v>
+        <v>0.4519976377487182</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0726764872670173</v>
+        <v>0.0755128040909767</v>
       </c>
       <c r="K4" t="n">
-        <v>66.88103699684143</v>
+        <v>67.4922981262207</v>
       </c>
       <c r="L4" t="n">
-        <v>1.93265151977539</v>
+        <v>1.668583154678345</v>
       </c>
       <c r="M4" t="n">
-        <v>9.733065366744995</v>
+        <v>9.098645210266112</v>
       </c>
       <c r="N4" t="n">
-        <v>11.84351658821106</v>
+        <v>12.36495304107666</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0644217173258463</v>
+        <v>0.0556194384892781</v>
       </c>
       <c r="P4" t="n">
-        <v>0.3244355122248332</v>
+        <v>0.3032881736755371</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.394783886273702</v>
+        <v>0.412165101369222</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250718-090229</t>
+          <t>20250721-144048</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1725,56 +1725,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>60</v>
+        <v>155</v>
       </c>
       <c r="C5" t="n">
-        <v>98.93816041946413</v>
+        <v>245.3161239624024</v>
       </c>
       <c r="D5" t="n">
         <v>3.059999942779541</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1516955092549323</v>
+        <v>0.1515789133887136</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3783194124698639</v>
+        <v>0.4339158833026886</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3858546614646911</v>
+        <v>0.4395067691802978</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3854338824748993</v>
+        <v>0.4392220973968506</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3790627717971802</v>
+        <v>0.4278211593627929</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0707963481545448</v>
+        <v>0.0850956737995147</v>
       </c>
       <c r="K5" t="n">
-        <v>61.28239011764526</v>
+        <v>67.59184241294861</v>
       </c>
       <c r="L5" t="n">
-        <v>1.648331642150879</v>
+        <v>1.665253400802612</v>
       </c>
       <c r="M5" t="n">
-        <v>9.517051458358765</v>
+        <v>9.102867603302002</v>
       </c>
       <c r="N5" t="n">
-        <v>11.57126593589783</v>
+        <v>12.30141806602478</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0549443880716959</v>
+        <v>0.0555084466934204</v>
       </c>
       <c r="P5" t="n">
-        <v>0.3172350486119588</v>
+        <v>0.3034289201100667</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.3857088645299276</v>
+        <v>0.4100472688674926</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250718-090559</t>
+          <t>20250721-144628</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1846,56 +1846,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>20</v>
+        <v>151</v>
       </c>
       <c r="C6" t="n">
-        <v>35.50347399711609</v>
+        <v>238.5289204120636</v>
       </c>
       <c r="D6" t="n">
         <v>3.059999942779541</v>
       </c>
       <c r="E6" t="n">
-        <v>0.151647450774908</v>
+        <v>0.1507834982595695</v>
       </c>
       <c r="F6" t="n">
-        <v>0.168219968676567</v>
+        <v>0.4599642157554626</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1730631291866302</v>
+        <v>0.4681966304779053</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1736255288124084</v>
+        <v>0.4675374627113342</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1659233570098877</v>
+        <v>0.4664440453052521</v>
       </c>
       <c r="J6" t="n">
-        <v>0.07776191830635069</v>
+        <v>0.0697616413235664</v>
       </c>
       <c r="K6" t="n">
-        <v>67.40379190444946</v>
+        <v>61.55367136001587</v>
       </c>
       <c r="L6" t="n">
-        <v>1.665375947952271</v>
+        <v>1.688873291015625</v>
       </c>
       <c r="M6" t="n">
-        <v>9.123697519302368</v>
+        <v>9.498602867126465</v>
       </c>
       <c r="N6" t="n">
-        <v>12.47004318237305</v>
+        <v>11.25373554229736</v>
       </c>
       <c r="O6" t="n">
-        <v>0.055512531598409</v>
+        <v>0.0562957763671875</v>
       </c>
       <c r="P6" t="n">
-        <v>0.3041232506434123</v>
+        <v>0.3166200955708821</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.4156681060791015</v>
+        <v>0.3751245180765787</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250718-091013</t>
+          <t>20250721-145310</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -2133,56 +2133,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32</v>
+        <v>115</v>
       </c>
       <c r="C2" t="n">
-        <v>46.78793907165527</v>
+        <v>157.8096179962158</v>
       </c>
       <c r="D2" t="n">
-        <v>1.440000057220459</v>
+        <v>1.679999947547913</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1227402123622596</v>
+        <v>0.124087604102881</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2207955420017242</v>
+        <v>0.3877297639846802</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2269479781389236</v>
+        <v>0.4016009569168091</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2270411849021911</v>
+        <v>0.4012927711009979</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1924721896648407</v>
+        <v>0.312138944864273</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0669071972370147</v>
+        <v>0.057769201695919</v>
       </c>
       <c r="K2" t="n">
-        <v>51.28772115707397</v>
+        <v>50.72141480445862</v>
       </c>
       <c r="L2" t="n">
-        <v>1.402185916900635</v>
+        <v>1.727756261825562</v>
       </c>
       <c r="M2" t="n">
-        <v>13.5505805015564</v>
+        <v>13.32420110702515</v>
       </c>
       <c r="N2" t="n">
-        <v>16.71355009078979</v>
+        <v>16.9546947479248</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0467395305633544</v>
+        <v>0.0575918753941853</v>
       </c>
       <c r="P2" t="n">
-        <v>0.4516860167185465</v>
+        <v>0.4441400369008382</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.5571183363596598</v>
+        <v>0.5651564915974935</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250718-150326</t>
+          <t>20250721-211505</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -2254,56 +2254,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>44</v>
+        <v>191</v>
       </c>
       <c r="C3" t="n">
-        <v>62.36910271644592</v>
+        <v>259.3788900375366</v>
       </c>
       <c r="D3" t="n">
-        <v>1.440000057220459</v>
+        <v>1.490000009536743</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1222115951505573</v>
+        <v>0.1236042554699937</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2518113851547241</v>
+        <v>0.4355120658874511</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2612974047660827</v>
+        <v>0.4403169155120849</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2613295912742615</v>
+        <v>0.439543604850769</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2256472408771515</v>
+        <v>0.3751641809940338</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0607125274837017</v>
+        <v>0.060871347784996</v>
       </c>
       <c r="K3" t="n">
-        <v>56.9702627658844</v>
+        <v>51.08053350448608</v>
       </c>
       <c r="L3" t="n">
-        <v>1.464324951171875</v>
+        <v>1.755584239959717</v>
       </c>
       <c r="M3" t="n">
-        <v>13.24821376800537</v>
+        <v>13.52181077003479</v>
       </c>
       <c r="N3" t="n">
-        <v>18.0265588760376</v>
+        <v>17.10185742378235</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0488108317057291</v>
+        <v>0.0585194746653238</v>
       </c>
       <c r="P3" t="n">
-        <v>0.441607125600179</v>
+        <v>0.4507270256678263</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.6008852958679199</v>
+        <v>0.5700619141260783</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250718-150646</t>
+          <t>20250721-212016</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -2375,56 +2375,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36</v>
+        <v>115</v>
       </c>
       <c r="C4" t="n">
-        <v>51.66034197807312</v>
+        <v>158.0307178497314</v>
       </c>
       <c r="D4" t="n">
-        <v>1.440000057220459</v>
+        <v>1.490000009536743</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1232822651250494</v>
+        <v>0.1229313615871512</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2376798391342163</v>
+        <v>0.406911551952362</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2676172852516174</v>
+        <v>0.4160818755626678</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2677917182445526</v>
+        <v>0.4153489172458648</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1979610919952392</v>
+        <v>0.3058168292045593</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0604877322912216</v>
+        <v>0.0667111054062843</v>
       </c>
       <c r="K4" t="n">
-        <v>56.51408267021179</v>
+        <v>57.01998519897461</v>
       </c>
       <c r="L4" t="n">
-        <v>1.442362785339356</v>
+        <v>1.719593286514282</v>
       </c>
       <c r="M4" t="n">
-        <v>13.83525156974792</v>
+        <v>13.17686676979065</v>
       </c>
       <c r="N4" t="n">
-        <v>16.67727589607239</v>
+        <v>17.66217184066772</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0480787595113118</v>
+        <v>0.0573197762171427</v>
       </c>
       <c r="P4" t="n">
-        <v>0.4611750523249308</v>
+        <v>0.439228892326355</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.5559091965357462</v>
+        <v>0.5887390613555908</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250718-151023</t>
+          <t>20250721-212709</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -2496,56 +2496,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40</v>
+        <v>171</v>
       </c>
       <c r="C5" t="n">
-        <v>57.88482165336609</v>
+        <v>229.6724796295166</v>
       </c>
       <c r="D5" t="n">
-        <v>1.450000047683716</v>
+        <v>1.490000009536743</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1240976203233003</v>
+        <v>0.1220509221243579</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2297760248184204</v>
+        <v>0.4190531969070434</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2367852330207824</v>
+        <v>0.4285716712474823</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2366120219230651</v>
+        <v>0.4285142123699188</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1022445112466812</v>
+        <v>0.3113705217838287</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0606279037892818</v>
+        <v>0.059785921126604</v>
       </c>
       <c r="K5" t="n">
-        <v>56.99233818054199</v>
+        <v>57.23772525787354</v>
       </c>
       <c r="L5" t="n">
-        <v>1.515407562255859</v>
+        <v>1.421677112579346</v>
       </c>
       <c r="M5" t="n">
-        <v>13.45753502845764</v>
+        <v>13.62222003936768</v>
       </c>
       <c r="N5" t="n">
-        <v>16.64229702949524</v>
+        <v>16.51462030410767</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0505135854085286</v>
+        <v>0.0473892370859781</v>
       </c>
       <c r="P5" t="n">
-        <v>0.448584500948588</v>
+        <v>0.4540740013122558</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.554743234316508</v>
+        <v>0.5504873434702555</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250718-151348</t>
+          <t>20250721-213220</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -2617,56 +2617,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>36</v>
+        <v>159</v>
       </c>
       <c r="C6" t="n">
-        <v>52.87658858299256</v>
+        <v>216.4825401306152</v>
       </c>
       <c r="D6" t="n">
-        <v>1.440000057220459</v>
+        <v>1.490000009536743</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1270229135536484</v>
+        <v>0.1240988826882913</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2256554961204528</v>
+        <v>0.415533572435379</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2267203330993652</v>
+        <v>0.4262629151344299</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2269483506679535</v>
+        <v>0.4256988763809204</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1760870814323425</v>
+        <v>0.2435154318809509</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0624355152249336</v>
+        <v>0.0613468810915946</v>
       </c>
       <c r="K6" t="n">
-        <v>56.4743390083313</v>
+        <v>50.91386198997498</v>
       </c>
       <c r="L6" t="n">
-        <v>1.51559591293335</v>
+        <v>1.471486568450928</v>
       </c>
       <c r="M6" t="n">
-        <v>13.75158405303955</v>
+        <v>13.56755495071411</v>
       </c>
       <c r="N6" t="n">
-        <v>16.72890281677246</v>
+        <v>17.78468322753906</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0505198637644449</v>
+        <v>0.0490495522816975</v>
       </c>
       <c r="P6" t="n">
-        <v>0.4583861351013183</v>
+        <v>0.4522518316904704</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.5576300938924154</v>
+        <v>0.592822774251302</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250718-151719</t>
+          <t>20250721-213844</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -2904,56 +2904,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>60</v>
+        <v>163</v>
       </c>
       <c r="C2" t="n">
-        <v>179.4314470291138</v>
+        <v>470.7588827610016</v>
       </c>
       <c r="D2" t="n">
-        <v>8.949999809265137</v>
+        <v>9.140000343322754</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3305132125814756</v>
+        <v>0.3288496750995425</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3001717031002044</v>
+        <v>0.3567015826702118</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3078881502151489</v>
+        <v>0.3734783828258514</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3071324527263641</v>
+        <v>0.3728648722171783</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1267274320125579</v>
+        <v>0.1704494208097458</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1184577494859695</v>
+        <v>0.1161496341228485</v>
       </c>
       <c r="K2" t="n">
-        <v>352.863795042038</v>
+        <v>347.9811408519745</v>
       </c>
       <c r="L2" t="n">
-        <v>2.719746112823486</v>
+        <v>2.424262046813965</v>
       </c>
       <c r="M2" t="n">
-        <v>13.47654557228088</v>
+        <v>12.86261177062988</v>
       </c>
       <c r="N2" t="n">
-        <v>20.81514549255371</v>
+        <v>20.92974019050598</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0906582037607828</v>
+        <v>0.08080873489379881</v>
       </c>
       <c r="P2" t="n">
-        <v>0.4492181857426961</v>
+        <v>0.4287537256876627</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.6938381830851237</v>
+        <v>0.6976580063501994</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250718-211635</t>
+          <t>20250722-041638</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -3025,56 +3025,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>52</v>
+        <v>199</v>
       </c>
       <c r="C3" t="n">
-        <v>158.457043170929</v>
+        <v>576.7528073787689</v>
       </c>
       <c r="D3" t="n">
-        <v>8.909999847412109</v>
+        <v>8.939999580383301</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3345538234481445</v>
+        <v>0.3288238926149492</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2964028418064117</v>
+        <v>0.4653829634189605</v>
       </c>
       <c r="G3" t="n">
-        <v>0.319589227437973</v>
+        <v>0.4758801460266113</v>
       </c>
       <c r="H3" t="n">
-        <v>0.319499522447586</v>
+        <v>0.475745290517807</v>
       </c>
       <c r="I3" t="n">
-        <v>0.103586308658123</v>
+        <v>0.0733666867017746</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1249542906880378</v>
+        <v>0.1168902888894081</v>
       </c>
       <c r="K3" t="n">
-        <v>377.5164985656738</v>
+        <v>359.5706536769867</v>
       </c>
       <c r="L3" t="n">
-        <v>2.760414838790894</v>
+        <v>2.628141641616821</v>
       </c>
       <c r="M3" t="n">
-        <v>12.86736965179443</v>
+        <v>13.50472688674927</v>
       </c>
       <c r="N3" t="n">
-        <v>22.63592147827148</v>
+        <v>21.43883538246155</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0920138279596964</v>
+        <v>0.0876047213872273</v>
       </c>
       <c r="P3" t="n">
-        <v>0.4289123217264811</v>
+        <v>0.4501575628916422</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.7545307159423829</v>
+        <v>0.7146278460820515</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250718-212718</t>
+          <t>20250722-043212</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -3146,56 +3146,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36</v>
+        <v>175</v>
       </c>
       <c r="C4" t="n">
-        <v>111.1485781669617</v>
+        <v>510.4000587463379</v>
       </c>
       <c r="D4" t="n">
-        <v>8.909999847412109</v>
+        <v>8.989999771118164</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3361198074287838</v>
+        <v>0.3321315477575574</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2190846502780914</v>
+        <v>0.4433458745479584</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2217263877391815</v>
+        <v>0.4527301490306854</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2216576933860778</v>
+        <v>0.4521786272525787</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0585801266133785</v>
+        <v>0.1779231578111648</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1168950051069259</v>
+        <v>0.1193539276719093</v>
       </c>
       <c r="K4" t="n">
-        <v>349.7344937324524</v>
+        <v>354.0791079998016</v>
       </c>
       <c r="L4" t="n">
-        <v>2.688814878463745</v>
+        <v>2.406745195388794</v>
       </c>
       <c r="M4" t="n">
-        <v>12.73774838447571</v>
+        <v>13.05171871185303</v>
       </c>
       <c r="N4" t="n">
-        <v>20.79278779029847</v>
+        <v>21.07298707962036</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0896271626154581</v>
+        <v>0.0802248398462931</v>
       </c>
       <c r="P4" t="n">
-        <v>0.4245916128158569</v>
+        <v>0.4350572903951009</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.693092926343282</v>
+        <v>0.702432902654012</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250718-213807</t>
+          <t>20250722-044940</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -3267,56 +3267,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>52</v>
+        <v>143</v>
       </c>
       <c r="C5" t="n">
-        <v>156.7468240261078</v>
+        <v>417.648966550827</v>
       </c>
       <c r="D5" t="n">
         <v>8.909999847412109</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3301479913867436</v>
+        <v>0.3280674629694932</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2738633453845978</v>
+        <v>0.4246771335601806</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2883166670799255</v>
+        <v>0.4382236003875732</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2876529991626739</v>
+        <v>0.4374697804450989</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1653838753700256</v>
+        <v>0.1246526464819908</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1132382377982139</v>
+        <v>0.123531088232994</v>
       </c>
       <c r="K5" t="n">
-        <v>350.0843920707703</v>
+        <v>354.3229873180389</v>
       </c>
       <c r="L5" t="n">
-        <v>2.777834415435791</v>
+        <v>2.462263345718384</v>
       </c>
       <c r="M5" t="n">
-        <v>13.46274256706238</v>
+        <v>13.35968971252441</v>
       </c>
       <c r="N5" t="n">
-        <v>21.08265447616577</v>
+        <v>20.88275408744812</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0925944805145263</v>
+        <v>0.0820754448572794</v>
       </c>
       <c r="P5" t="n">
-        <v>0.4487580855687459</v>
+        <v>0.4453229904174804</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.7027551492055257</v>
+        <v>0.6960918029149373</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250718-214744</t>
+          <t>20250722-050554</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -3388,56 +3388,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>24</v>
+        <v>131</v>
       </c>
       <c r="C6" t="n">
-        <v>74.70913982391357</v>
+        <v>384.5315132141113</v>
       </c>
       <c r="D6" t="n">
         <v>8.909999847412109</v>
       </c>
       <c r="E6" t="n">
-        <v>0.328757689644893</v>
+        <v>0.3343267627344786</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1811384111642837</v>
+        <v>0.4306296110153198</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1817440390586853</v>
+        <v>0.4394509792327881</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1815578043460846</v>
+        <v>0.4390569031238556</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1168839856982231</v>
+        <v>0.1441414505243301</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1119240149855613</v>
+        <v>0.1203108802437782</v>
       </c>
       <c r="K6" t="n">
-        <v>349.8526771068573</v>
+        <v>356.6308779716492</v>
       </c>
       <c r="L6" t="n">
-        <v>2.693390607833862</v>
+        <v>2.405103445053101</v>
       </c>
       <c r="M6" t="n">
-        <v>13.06260204315186</v>
+        <v>13.33915710449219</v>
       </c>
       <c r="N6" t="n">
-        <v>20.70151233673096</v>
+        <v>21.07949042320251</v>
       </c>
       <c r="O6" t="n">
-        <v>0.08977968692779539</v>
+        <v>0.08017011483510331</v>
       </c>
       <c r="P6" t="n">
-        <v>0.4354200681050618</v>
+        <v>0.4446385701497395</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.6900504112243653</v>
+        <v>0.7026496807734172</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250718-215806</t>
+          <t>20250722-052036</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -3675,56 +3675,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>60</v>
+        <v>135</v>
       </c>
       <c r="C2" t="n">
-        <v>130.5854578018188</v>
+        <v>287.8934514522552</v>
       </c>
       <c r="D2" t="n">
-        <v>7.78000020980835</v>
+        <v>7.769999980926514</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1990370931724707</v>
+        <v>0.1993683946353417</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2517269551753998</v>
+        <v>0.4543249011039734</v>
       </c>
       <c r="G2" t="n">
-        <v>0.261653184890747</v>
+        <v>0.4648369252681732</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2616105675697326</v>
+        <v>0.4643973112106323</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2272599637508392</v>
+        <v>0.4257616698741913</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0838040634989738</v>
+        <v>0.0858613774180412</v>
       </c>
       <c r="K2" t="n">
-        <v>48.14171886444092</v>
+        <v>42.2426347732544</v>
       </c>
       <c r="L2" t="n">
-        <v>2.002895355224609</v>
+        <v>2.009660720825196</v>
       </c>
       <c r="M2" t="n">
-        <v>10.80359601974487</v>
+        <v>10.54833555221558</v>
       </c>
       <c r="N2" t="n">
-        <v>12.47163772583008</v>
+        <v>12.20176815986633</v>
       </c>
       <c r="O2" t="n">
-        <v>0.06676317850748691</v>
+        <v>0.0669886906941731</v>
       </c>
       <c r="P2" t="n">
-        <v>0.3601198673248291</v>
+        <v>0.3516111850738525</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.4157212575276692</v>
+        <v>0.4067256053288777</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250719-133842</t>
+          <t>20250722-214104</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -3796,56 +3796,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>56</v>
+        <v>199</v>
       </c>
       <c r="C3" t="n">
-        <v>121.9080450534821</v>
+        <v>415.6593923568726</v>
       </c>
       <c r="D3" t="n">
         <v>7.769999980926514</v>
       </c>
       <c r="E3" t="n">
-        <v>0.198766111263207</v>
+        <v>0.1986587433958772</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2848607301712036</v>
+        <v>0.5159934759140015</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2877472937107086</v>
+        <v>0.5181714296340942</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2879523038864136</v>
+        <v>0.5178666114807129</v>
       </c>
       <c r="I3" t="n">
-        <v>0.26792773604393</v>
+        <v>0.5146176815032959</v>
       </c>
       <c r="J3" t="n">
-        <v>0.08587080985307689</v>
+        <v>0.0852264687418937</v>
       </c>
       <c r="K3" t="n">
-        <v>42.3604793548584</v>
+        <v>48.59032249450684</v>
       </c>
       <c r="L3" t="n">
-        <v>1.955503463745117</v>
+        <v>2.306709289550781</v>
       </c>
       <c r="M3" t="n">
-        <v>10.43646502494812</v>
+        <v>10.23885655403137</v>
       </c>
       <c r="N3" t="n">
-        <v>11.91979598999023</v>
+        <v>12.08794212341309</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0651834487915039</v>
+        <v>0.0768903096516927</v>
       </c>
       <c r="P3" t="n">
-        <v>0.3478821674982706</v>
+        <v>0.3412952184677124</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.3973265329996744</v>
+        <v>0.4029314041137695</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250719-134308</t>
+          <t>20250722-214807</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -3917,56 +3917,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>84</v>
+        <v>199</v>
       </c>
       <c r="C4" t="n">
-        <v>181.0660026073456</v>
+        <v>413.8655033111572</v>
       </c>
       <c r="D4" t="n">
         <v>7.769999980926514</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1981565125641368</v>
+        <v>0.1994933634247612</v>
       </c>
       <c r="F4" t="n">
-        <v>0.416887491941452</v>
+        <v>0.4960216283798218</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4222943782806396</v>
+        <v>0.5034060478210449</v>
       </c>
       <c r="H4" t="n">
-        <v>0.421707808971405</v>
+        <v>0.5027398467063904</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4191970229148865</v>
+        <v>0.5017250776290894</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0848196372389793</v>
+        <v>0.0859450027346611</v>
       </c>
       <c r="K4" t="n">
-        <v>42.07991600036621</v>
+        <v>48.21240305900574</v>
       </c>
       <c r="L4" t="n">
-        <v>2.06041145324707</v>
+        <v>2.314360618591309</v>
       </c>
       <c r="M4" t="n">
-        <v>10.17653346061706</v>
+        <v>9.49003791809082</v>
       </c>
       <c r="N4" t="n">
-        <v>12.75722932815552</v>
+        <v>11.85963702201843</v>
       </c>
       <c r="O4" t="n">
-        <v>0.06868038177490229</v>
+        <v>0.0771453539530436</v>
       </c>
       <c r="P4" t="n">
-        <v>0.3392177820205688</v>
+        <v>0.316334597269694</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.4252409776051839</v>
+        <v>0.3953212340672811</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250719-134724</t>
+          <t>20250722-215718</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -4038,56 +4038,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40</v>
+        <v>199</v>
       </c>
       <c r="C5" t="n">
-        <v>88.22235488891602</v>
+        <v>414.8754255771637</v>
       </c>
       <c r="D5" t="n">
         <v>7.769999980926514</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1988526985049247</v>
+        <v>0.1995544704660099</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1719351261854171</v>
+        <v>0.5097984075546265</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1817498505115509</v>
+        <v>0.510701596736908</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1816181093454361</v>
+        <v>0.5097808241844177</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1674363911151886</v>
+        <v>0.5033535957336426</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0848665088415145</v>
+        <v>0.082125648856163</v>
       </c>
       <c r="K5" t="n">
-        <v>48.35477375984192</v>
+        <v>48.68040800094604</v>
       </c>
       <c r="L5" t="n">
-        <v>2.019634246826172</v>
+        <v>1.964924573898316</v>
       </c>
       <c r="M5" t="n">
-        <v>10.55477476119995</v>
+        <v>10.56878161430359</v>
       </c>
       <c r="N5" t="n">
-        <v>11.7294774055481</v>
+        <v>12.18898844718933</v>
       </c>
       <c r="O5" t="n">
-        <v>0.06732114156087229</v>
+        <v>0.06549748579661049</v>
       </c>
       <c r="P5" t="n">
-        <v>0.3518258253733317</v>
+        <v>0.3522927204767863</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.3909825801849365</v>
+        <v>0.406299614906311</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250719-135240</t>
+          <t>20250722-220627</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -4159,56 +4159,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>72</v>
+        <v>199</v>
       </c>
       <c r="C6" t="n">
-        <v>156.397878408432</v>
+        <v>414.5005478858948</v>
       </c>
       <c r="D6" t="n">
         <v>7.769999980926514</v>
       </c>
       <c r="E6" t="n">
-        <v>0.19890750799742</v>
+        <v>0.1989960513971558</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3612143993377685</v>
+        <v>0.5142396688461304</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3658285140991211</v>
+        <v>0.5078930854797363</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3656815886497497</v>
+        <v>0.507287859916687</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3463213443756103</v>
+        <v>0.4802863001823425</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0831448212265968</v>
+        <v>0.0857481658458709</v>
       </c>
       <c r="K6" t="n">
-        <v>48.20614147186279</v>
+        <v>48.24604415893555</v>
       </c>
       <c r="L6" t="n">
-        <v>2.352224588394165</v>
+        <v>2.263290643692017</v>
       </c>
       <c r="M6" t="n">
-        <v>10.3447048664093</v>
+        <v>10.24585270881653</v>
       </c>
       <c r="N6" t="n">
-        <v>12.02212619781494</v>
+        <v>12.1384494304657</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0784074862798055</v>
+        <v>0.0754430214564005</v>
       </c>
       <c r="P6" t="n">
-        <v>0.3448234955469767</v>
+        <v>0.3415284236272176</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.4007375399271647</v>
+        <v>0.4046149810155233</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250719-135622</t>
+          <t>20250722-221538</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -4446,56 +4446,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>52</v>
+        <v>199</v>
       </c>
       <c r="C2" t="n">
-        <v>76.01842427253723</v>
+        <v>276.9131126403809</v>
       </c>
       <c r="D2" t="n">
-        <v>4.659999847412109</v>
+        <v>4.670000076293945</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1188945221499754</v>
+        <v>0.1197696799534049</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1599507480859756</v>
+        <v>0.4516727328300476</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1625731140375137</v>
+        <v>0.4585943818092346</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1623952090740203</v>
+        <v>0.4579297602176666</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1627833098173141</v>
+        <v>0.4567763209342956</v>
       </c>
       <c r="J2" t="n">
-        <v>0.061225701123476</v>
+        <v>0.0596217326819896</v>
       </c>
       <c r="K2" t="n">
-        <v>30.05169463157653</v>
+        <v>24.52042198181152</v>
       </c>
       <c r="L2" t="n">
-        <v>1.386127710342407</v>
+        <v>1.458928108215332</v>
       </c>
       <c r="M2" t="n">
-        <v>8.008608818054199</v>
+        <v>8.61059308052063</v>
       </c>
       <c r="N2" t="n">
-        <v>9.229219436645508</v>
+        <v>9.282186031341553</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0462042570114135</v>
+        <v>0.048630936940511</v>
       </c>
       <c r="P2" t="n">
-        <v>0.2669536272684733</v>
+        <v>0.2870197693506877</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.3076406478881835</v>
+        <v>0.3094062010447184</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250719-200203</t>
+          <t>20250723-050602</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -4567,56 +4567,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>32</v>
+        <v>199</v>
       </c>
       <c r="C3" t="n">
-        <v>48.88620281219482</v>
+        <v>277.6002380847931</v>
       </c>
       <c r="D3" t="n">
-        <v>4.670000076293945</v>
+        <v>4.659999847412109</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1193703850731253</v>
+        <v>0.1194024469010793</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1342638731002807</v>
+        <v>0.4550323486328125</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1427924335002899</v>
+        <v>0.4631520807743072</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1426872760057449</v>
+        <v>0.4619094133377075</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1450531780719757</v>
+        <v>0.4572015702724457</v>
       </c>
       <c r="J3" t="n">
-        <v>0.059993028640747</v>
+        <v>0.062624916434288</v>
       </c>
       <c r="K3" t="n">
-        <v>24.96024608612061</v>
+        <v>24.45741987228394</v>
       </c>
       <c r="L3" t="n">
-        <v>1.656467437744141</v>
+        <v>1.419211149215698</v>
       </c>
       <c r="M3" t="n">
-        <v>8.685084104537964</v>
+        <v>8.746687650680542</v>
       </c>
       <c r="N3" t="n">
-        <v>9.083806753158569</v>
+        <v>9.694059371948242</v>
       </c>
       <c r="O3" t="n">
-        <v>0.055215581258138</v>
+        <v>0.0473070383071899</v>
       </c>
       <c r="P3" t="n">
-        <v>0.2895028034845988</v>
+        <v>0.2915562550226847</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.302793558438619</v>
+        <v>0.3231353123982747</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250719-200501</t>
+          <t>20250723-051221</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -4688,56 +4688,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>56</v>
+        <v>199</v>
       </c>
       <c r="C4" t="n">
-        <v>82.21870684623718</v>
+        <v>282.1773478984833</v>
       </c>
       <c r="D4" t="n">
         <v>4.670000076293945</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1199040306465965</v>
+        <v>0.120203617417333</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1689963042736053</v>
+        <v>0.4610125422477722</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1883372515439987</v>
+        <v>0.4711236655712127</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1887300163507461</v>
+        <v>0.4704625606536865</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1873496174812317</v>
+        <v>0.4687630832195282</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0608474239706993</v>
+        <v>0.0588224567472934</v>
       </c>
       <c r="K4" t="n">
-        <v>29.85995316505432</v>
+        <v>30.53815245628357</v>
       </c>
       <c r="L4" t="n">
-        <v>1.382637739181519</v>
+        <v>1.471336126327515</v>
       </c>
       <c r="M4" t="n">
-        <v>8.504799604415894</v>
+        <v>8.413454532623291</v>
       </c>
       <c r="N4" t="n">
-        <v>10.0040340423584</v>
+        <v>9.216334819793699</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0460879246393839</v>
+        <v>0.0490445375442504</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2834933201471964</v>
+        <v>0.2804484844207763</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.3334678014119466</v>
+        <v>0.30721116065979</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250719-200732</t>
+          <t>20250723-051842</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -4809,56 +4809,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>48</v>
+        <v>199</v>
       </c>
       <c r="C5" t="n">
-        <v>71.23527598381042</v>
+        <v>279.8525333404541</v>
       </c>
       <c r="D5" t="n">
-        <v>4.659999847412109</v>
+        <v>4.670000076293945</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1191580719314515</v>
+        <v>0.1192803057144634</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1634296327829361</v>
+        <v>0.4508427381515503</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1686016470193863</v>
+        <v>0.4576118886470794</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1686245799064636</v>
+        <v>0.4572312831878662</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1695459336042404</v>
+        <v>0.4568933248519897</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0605977997183799</v>
+        <v>0.0595764629542827</v>
       </c>
       <c r="K5" t="n">
-        <v>29.97423362731934</v>
+        <v>30.23016834259033</v>
       </c>
       <c r="L5" t="n">
-        <v>1.44914436340332</v>
+        <v>1.482845067977905</v>
       </c>
       <c r="M5" t="n">
-        <v>8.003356456756592</v>
+        <v>8.39039421081543</v>
       </c>
       <c r="N5" t="n">
-        <v>9.453309535980225</v>
+        <v>9.619868993759155</v>
       </c>
       <c r="O5" t="n">
-        <v>0.048304812113444</v>
+        <v>0.0494281689325968</v>
       </c>
       <c r="P5" t="n">
-        <v>0.266778548558553</v>
+        <v>0.279679807027181</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.3151103178660074</v>
+        <v>0.3206622997919718</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250719-201018</t>
+          <t>20250723-052507</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -4930,56 +4930,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>28</v>
+        <v>199</v>
       </c>
       <c r="C6" t="n">
-        <v>43.30517172813416</v>
+        <v>278.3252182006836</v>
       </c>
       <c r="D6" t="n">
-        <v>4.659999847412109</v>
+        <v>4.670000076293945</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1194496694952249</v>
+        <v>0.1196486596860477</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1144793182611465</v>
+        <v>0.4496654868125915</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1210009157657623</v>
+        <v>0.457512229681015</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1210547313094139</v>
+        <v>0.4572270512580871</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1205882802605629</v>
+        <v>0.4570146203041076</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0633328929543495</v>
+        <v>0.0597833469510078</v>
       </c>
       <c r="K6" t="n">
-        <v>24.50400424003601</v>
+        <v>29.94098138809204</v>
       </c>
       <c r="L6" t="n">
-        <v>1.700155019760132</v>
+        <v>1.448460102081299</v>
       </c>
       <c r="M6" t="n">
-        <v>8.279247522354126</v>
+        <v>8.527717351913452</v>
       </c>
       <c r="N6" t="n">
-        <v>9.620832681655884</v>
+        <v>9.543805360794067</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0566718339920043</v>
+        <v>0.0482820034027099</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2759749174118042</v>
+        <v>0.2842572450637817</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.3206944227218627</v>
+        <v>0.3181268453598022</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250719-201311</t>
+          <t>20250723-053130</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -5217,56 +5217,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>20</v>
+        <v>199</v>
       </c>
       <c r="C2" t="n">
-        <v>27.41730213165283</v>
+        <v>243.9782917499543</v>
       </c>
       <c r="D2" t="n">
-        <v>3.509999990463257</v>
+        <v>3.559999942779541</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1051087640225886</v>
+        <v>0.1060908343549349</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0597583651542663</v>
+        <v>0.353611558675766</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0610887594521045</v>
+        <v>0.3631458878517151</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0609752684831619</v>
+        <v>0.3627616763114929</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0604841113090515</v>
+        <v>0.361910879611969</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0533258132636547</v>
+        <v>0.056023009121418</v>
       </c>
       <c r="K2" t="n">
-        <v>26.83817148208618</v>
+        <v>27.9010112285614</v>
       </c>
       <c r="L2" t="n">
-        <v>1.313525438308716</v>
+        <v>1.283884763717651</v>
       </c>
       <c r="M2" t="n">
-        <v>8.775502920150757</v>
+        <v>7.940499067306519</v>
       </c>
       <c r="N2" t="n">
-        <v>9.85105562210083</v>
+        <v>9.345071315765381</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0437841812769571</v>
+        <v>0.0427961587905883</v>
       </c>
       <c r="P2" t="n">
-        <v>0.2925167640050252</v>
+        <v>0.2646833022435506</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.3283685207366943</v>
+        <v>0.3115023771921794</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250720-002434</t>
+          <t>20250723-103716</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -5338,56 +5338,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>72</v>
+        <v>199</v>
       </c>
       <c r="C3" t="n">
-        <v>91.27635478973389</v>
+        <v>244.5525705814362</v>
       </c>
       <c r="D3" t="n">
         <v>3.509999990463257</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1066085601018534</v>
+        <v>0.1063803587501971</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1605273187160492</v>
+        <v>0.4027910530567169</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1665329486131668</v>
+        <v>0.4145886898040771</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1667248755693435</v>
+        <v>0.4140364527702331</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1659938693046569</v>
+        <v>0.4109764099121094</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0521037727594375</v>
+        <v>0.0541571602225303</v>
       </c>
       <c r="K3" t="n">
-        <v>21.38771510124207</v>
+        <v>26.69606995582581</v>
       </c>
       <c r="L3" t="n">
-        <v>1.319232702255249</v>
+        <v>1.282923698425293</v>
       </c>
       <c r="M3" t="n">
-        <v>8.167494058609009</v>
+        <v>8.451106548309326</v>
       </c>
       <c r="N3" t="n">
-        <v>10.40548133850098</v>
+        <v>9.683286666870115</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0439744234085083</v>
+        <v>0.0427641232808431</v>
       </c>
       <c r="P3" t="n">
-        <v>0.2722498019536336</v>
+        <v>0.2817035516103108</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.3468493779500325</v>
+        <v>0.3227762222290039</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250720-002642</t>
+          <t>20250723-104300</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -5459,56 +5459,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>40</v>
+        <v>199</v>
       </c>
       <c r="C4" t="n">
-        <v>51.20920085906982</v>
+        <v>243.4162364006042</v>
       </c>
       <c r="D4" t="n">
         <v>3.509999990463257</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1043710872530936</v>
+        <v>0.1050921701381553</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1160942018032074</v>
+        <v>0.4100384712219238</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1215138584375381</v>
+        <v>0.4158837795257568</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1214422881603241</v>
+        <v>0.4154682755470276</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1224136501550674</v>
+        <v>0.4166941940784454</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0528568252921104</v>
+        <v>0.0549046844244003</v>
       </c>
       <c r="K4" t="n">
-        <v>26.62878060340881</v>
+        <v>27.44565725326538</v>
       </c>
       <c r="L4" t="n">
-        <v>1.276059865951538</v>
+        <v>1.302720069885254</v>
       </c>
       <c r="M4" t="n">
-        <v>8.045118808746338</v>
+        <v>8.220870018005371</v>
       </c>
       <c r="N4" t="n">
-        <v>9.876879453659058</v>
+        <v>9.741946220397949</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0425353288650512</v>
+        <v>0.0434240023295084</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2681706269582112</v>
+        <v>0.274029000600179</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.3292293151219685</v>
+        <v>0.3247315406799316</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250720-002934</t>
+          <t>20250723-104845</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -5580,56 +5580,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>20</v>
+        <v>199</v>
       </c>
       <c r="C5" t="n">
-        <v>27.74294757843018</v>
+        <v>242.5878963470459</v>
       </c>
       <c r="D5" t="n">
         <v>3.509999990463257</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1047015648335218</v>
+        <v>0.1061091567927868</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0759712308645248</v>
+        <v>0.3916984796524048</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0833161994814872</v>
+        <v>0.4037482142448425</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0832781195640564</v>
+        <v>0.4037676155567169</v>
       </c>
       <c r="I5" t="n">
-        <v>0.083495020866394</v>
+        <v>0.4052606225013733</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0515838451683521</v>
+        <v>0.0516676120460033</v>
       </c>
       <c r="K5" t="n">
-        <v>26.70889115333557</v>
+        <v>26.87655901908875</v>
       </c>
       <c r="L5" t="n">
-        <v>1.591989040374756</v>
+        <v>1.245183944702148</v>
       </c>
       <c r="M5" t="n">
-        <v>8.635213136672974</v>
+        <v>8.051016807556152</v>
       </c>
       <c r="N5" t="n">
-        <v>9.812734127044678</v>
+        <v>9.45614457130432</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0530663013458252</v>
+        <v>0.0415061314900716</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2878404378890991</v>
+        <v>0.2683672269185384</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.3270911375681559</v>
+        <v>0.3152048190434773</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250720-003206</t>
+          <t>20250723-105428</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -5701,56 +5701,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>36</v>
+        <v>199</v>
       </c>
       <c r="C6" t="n">
-        <v>46.58230495452881</v>
+        <v>244.1600046157837</v>
       </c>
       <c r="D6" t="n">
         <v>3.509999990463257</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1039475471609168</v>
+        <v>0.1065269084506897</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1180523186922073</v>
+        <v>0.3702768087387085</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1227759569883346</v>
+        <v>0.3816520869731903</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1224845722317695</v>
+        <v>0.3810664415359497</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1220573410391807</v>
+        <v>0.3817127048969269</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0516644157469272</v>
+        <v>0.0524094738066196</v>
       </c>
       <c r="K6" t="n">
-        <v>26.81454372406006</v>
+        <v>26.85162997245789</v>
       </c>
       <c r="L6" t="n">
-        <v>1.277306318283081</v>
+        <v>1.235166788101196</v>
       </c>
       <c r="M6" t="n">
-        <v>8.147143125534058</v>
+        <v>7.943443059921265</v>
       </c>
       <c r="N6" t="n">
-        <v>9.645028352737429</v>
+        <v>9.32031512260437</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0425768772761027</v>
+        <v>0.0411722262700398</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2715714375178019</v>
+        <v>0.2647814353307088</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.3215009450912475</v>
+        <v>0.310677170753479</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250720-003414</t>
+          <t>20250723-110011</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
